--- a/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B02_Normal_1.xlsx
+++ b/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B02_Normal_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J426"/>
+  <dimension ref="A1:K426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Segment_ID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Area</t>
         </is>
       </c>
@@ -515,6 +520,9 @@
         </is>
       </c>
       <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
         <v>24.44938674448072</v>
       </c>
     </row>
@@ -553,6 +561,9 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -591,6 +602,9 @@
         </is>
       </c>
       <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -629,6 +643,9 @@
         </is>
       </c>
       <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -667,6 +684,9 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
         <v>16.22537890841612</v>
       </c>
     </row>
@@ -705,6 +725,9 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
         <v>15.92519383307983</v>
       </c>
     </row>
@@ -743,6 +766,9 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
         <v>15.55123726155539</v>
       </c>
     </row>
@@ -781,6 +807,9 @@
         </is>
       </c>
       <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
         <v>15.50392193361757</v>
       </c>
     </row>
@@ -819,6 +848,9 @@
         </is>
       </c>
       <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
         <v>15.43409332138252</v>
       </c>
     </row>
@@ -857,6 +889,9 @@
         </is>
       </c>
       <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
         <v>15.43409332138252</v>
       </c>
     </row>
@@ -895,6 +930,9 @@
         </is>
       </c>
       <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
         <v>14.91383648998964</v>
       </c>
     </row>
@@ -933,6 +971,9 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
         <v>14.91383648998964</v>
       </c>
     </row>
@@ -971,6 +1012,9 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
         <v>13.96252814601202</v>
       </c>
     </row>
@@ -1009,6 +1053,9 @@
         </is>
       </c>
       <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
         <v>12.8845474029381</v>
       </c>
     </row>
@@ -1047,6 +1094,9 @@
         </is>
       </c>
       <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
         <v>12.56557511094277</v>
       </c>
     </row>
@@ -1085,6 +1135,9 @@
         </is>
       </c>
       <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
         <v>12.56557511094277</v>
       </c>
     </row>
@@ -1123,6 +1176,9 @@
         </is>
       </c>
       <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
         <v>12.42650727241244</v>
       </c>
     </row>
@@ -1161,6 +1217,9 @@
         </is>
       </c>
       <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
         <v>12.61222121789064</v>
       </c>
     </row>
@@ -1199,6 +1258,9 @@
         </is>
       </c>
       <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
         <v>12.6149723565889</v>
       </c>
     </row>
@@ -1237,6 +1299,9 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
         <v>12.6149723565889</v>
       </c>
     </row>
@@ -1275,6 +1340,9 @@
         </is>
       </c>
       <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
         <v>12.88726856229838</v>
       </c>
     </row>
@@ -1313,6 +1381,9 @@
         </is>
       </c>
       <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
         <v>13.08268414389388</v>
       </c>
     </row>
@@ -1351,6 +1422,9 @@
         </is>
       </c>
       <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
         <v>13.11655963642752</v>
       </c>
     </row>
@@ -1389,6 +1463,9 @@
         </is>
       </c>
       <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
         <v>13.06477406907523</v>
       </c>
     </row>
@@ -1427,6 +1504,9 @@
         </is>
       </c>
       <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
         <v>13.00822550737505</v>
       </c>
     </row>
@@ -1465,6 +1545,9 @@
         </is>
       </c>
       <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
         <v>13.00822550737505</v>
       </c>
     </row>
@@ -1503,6 +1586,9 @@
         </is>
       </c>
       <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
         <v>12.82946633796654</v>
       </c>
     </row>
@@ -1541,6 +1627,9 @@
         </is>
       </c>
       <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
         <v>12.72199060197538</v>
       </c>
     </row>
@@ -1579,6 +1668,9 @@
         </is>
       </c>
       <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
         <v>12.76786570293602</v>
       </c>
     </row>
@@ -1617,6 +1709,9 @@
         </is>
       </c>
       <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
         <v>12.94918332241907</v>
       </c>
     </row>
@@ -1655,6 +1750,9 @@
         </is>
       </c>
       <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
         <v>13.29202663846189</v>
       </c>
     </row>
@@ -1693,6 +1791,9 @@
         </is>
       </c>
       <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
         <v>13.29202663846189</v>
       </c>
     </row>
@@ -1731,6 +1832,9 @@
         </is>
       </c>
       <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
         <v>13.74461230569916</v>
       </c>
     </row>
@@ -1769,6 +1873,9 @@
         </is>
       </c>
       <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
         <v>14.01711486461985</v>
       </c>
     </row>
@@ -1807,6 +1914,9 @@
         </is>
       </c>
       <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
         <v>14.02341868198291</v>
       </c>
     </row>
@@ -1845,6 +1955,9 @@
         </is>
       </c>
       <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
         <v>14.4136984000467</v>
       </c>
     </row>
@@ -1883,6 +1996,9 @@
         </is>
       </c>
       <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
         <v>14.4136984000467</v>
       </c>
     </row>
@@ -1921,6 +2037,9 @@
         </is>
       </c>
       <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
         <v>14.4136984000467</v>
       </c>
     </row>
@@ -1959,6 +2078,9 @@
         </is>
       </c>
       <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
         <v>14.37286417316269</v>
       </c>
     </row>
@@ -1997,6 +2119,9 @@
         </is>
       </c>
       <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
         <v>14.36056284287022</v>
       </c>
     </row>
@@ -2035,6 +2160,9 @@
         </is>
       </c>
       <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
         <v>14.32918239439808</v>
       </c>
     </row>
@@ -2073,6 +2201,9 @@
         </is>
       </c>
       <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
         <v>14.33140447444988</v>
       </c>
     </row>
@@ -2111,6 +2242,9 @@
         </is>
       </c>
       <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
         <v>14.33266758623184</v>
       </c>
     </row>
@@ -2149,6 +2283,9 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" t="n">
         <v>14.47432312940295</v>
       </c>
     </row>
@@ -2187,6 +2324,9 @@
         </is>
       </c>
       <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
         <v>14.69408070284003</v>
       </c>
     </row>
@@ -2225,6 +2365,9 @@
         </is>
       </c>
       <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
         <v>14.90097207929845</v>
       </c>
     </row>
@@ -2263,6 +2406,9 @@
         </is>
       </c>
       <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
         <v>14.90097207929845</v>
       </c>
     </row>
@@ -2301,6 +2447,9 @@
         </is>
       </c>
       <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
         <v>15.39058793177672</v>
       </c>
     </row>
@@ -2339,6 +2488,9 @@
         </is>
       </c>
       <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="n">
         <v>15.55279586015389</v>
       </c>
     </row>
@@ -2377,6 +2529,9 @@
         </is>
       </c>
       <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
         <v>16.46410452789935</v>
       </c>
     </row>
@@ -2415,6 +2570,9 @@
         </is>
       </c>
       <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
         <v>17.37544874440357</v>
       </c>
     </row>
@@ -2453,6 +2611,9 @@
         </is>
       </c>
       <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
         <v>18.99504856873714</v>
       </c>
     </row>
@@ -2491,6 +2652,9 @@
         </is>
       </c>
       <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
         <v>19.35440687995326</v>
       </c>
     </row>
@@ -2529,6 +2693,9 @@
         </is>
       </c>
       <c r="J55" t="n">
+        <v>11</v>
+      </c>
+      <c r="K55" t="n">
         <v>20.85858809627996</v>
       </c>
     </row>
@@ -2567,6 +2734,9 @@
         </is>
       </c>
       <c r="J56" t="n">
+        <v>11</v>
+      </c>
+      <c r="K56" t="n">
         <v>20.89169658899361</v>
       </c>
     </row>
@@ -2605,6 +2775,9 @@
         </is>
       </c>
       <c r="J57" t="n">
+        <v>11</v>
+      </c>
+      <c r="K57" t="n">
         <v>21.75595998124422</v>
       </c>
     </row>
@@ -2643,6 +2816,9 @@
         </is>
       </c>
       <c r="J58" t="n">
+        <v>11</v>
+      </c>
+      <c r="K58" t="n">
         <v>22.23426731578168</v>
       </c>
     </row>
@@ -2681,6 +2857,9 @@
         </is>
       </c>
       <c r="J59" t="n">
+        <v>11</v>
+      </c>
+      <c r="K59" t="n">
         <v>21.95138014089535</v>
       </c>
     </row>
@@ -2719,6 +2898,9 @@
         </is>
       </c>
       <c r="J60" t="n">
+        <v>11</v>
+      </c>
+      <c r="K60" t="n">
         <v>24.63649424087505</v>
       </c>
     </row>
@@ -2757,6 +2939,9 @@
         </is>
       </c>
       <c r="J61" t="n">
+        <v>11</v>
+      </c>
+      <c r="K61" t="n">
         <v>25.18536911583633</v>
       </c>
     </row>
@@ -2795,6 +2980,9 @@
         </is>
       </c>
       <c r="J62" t="n">
+        <v>11</v>
+      </c>
+      <c r="K62" t="n">
         <v>27.31329478260586</v>
       </c>
     </row>
@@ -2833,6 +3021,9 @@
         </is>
       </c>
       <c r="J63" t="n">
+        <v>11</v>
+      </c>
+      <c r="K63" t="n">
         <v>27.18205504873007</v>
       </c>
     </row>
@@ -2871,6 +3062,9 @@
         </is>
       </c>
       <c r="J64" t="n">
+        <v>11</v>
+      </c>
+      <c r="K64" t="n">
         <v>26.71182468007363</v>
       </c>
     </row>
@@ -2909,6 +3103,9 @@
         </is>
       </c>
       <c r="J65" t="n">
+        <v>11</v>
+      </c>
+      <c r="K65" t="n">
         <v>26.61477337250786</v>
       </c>
     </row>
@@ -2947,6 +3144,9 @@
         </is>
       </c>
       <c r="J66" t="n">
+        <v>11</v>
+      </c>
+      <c r="K66" t="n">
         <v>9.819882390104297</v>
       </c>
     </row>
@@ -2985,6 +3185,9 @@
         </is>
       </c>
       <c r="J67" t="n">
+        <v>11</v>
+      </c>
+      <c r="K67" t="n">
         <v>9.819882390104297</v>
       </c>
     </row>
@@ -3023,6 +3226,9 @@
         </is>
       </c>
       <c r="J68" t="n">
+        <v>11</v>
+      </c>
+      <c r="K68" t="n">
         <v>9.745667235392832</v>
       </c>
     </row>
@@ -3061,6 +3267,9 @@
         </is>
       </c>
       <c r="J69" t="n">
+        <v>11</v>
+      </c>
+      <c r="K69" t="n">
         <v>9.745667235392832</v>
       </c>
     </row>
@@ -3099,6 +3308,9 @@
         </is>
       </c>
       <c r="J70" t="n">
+        <v>11</v>
+      </c>
+      <c r="K70" t="n">
         <v>9.75609596068019</v>
       </c>
     </row>
@@ -3137,6 +3349,9 @@
         </is>
       </c>
       <c r="J71" t="n">
+        <v>11</v>
+      </c>
+      <c r="K71" t="n">
         <v>9.75609596068019</v>
       </c>
     </row>
@@ -3175,6 +3390,9 @@
         </is>
       </c>
       <c r="J72" t="n">
+        <v>11</v>
+      </c>
+      <c r="K72" t="n">
         <v>9.981290382682612</v>
       </c>
     </row>
@@ -3213,6 +3431,9 @@
         </is>
       </c>
       <c r="J73" t="n">
+        <v>11</v>
+      </c>
+      <c r="K73" t="n">
         <v>9.981290382682612</v>
       </c>
     </row>
@@ -3251,6 +3472,9 @@
         </is>
       </c>
       <c r="J74" t="n">
+        <v>11</v>
+      </c>
+      <c r="K74" t="n">
         <v>12.09167051507188</v>
       </c>
     </row>
@@ -3289,6 +3513,9 @@
         </is>
       </c>
       <c r="J75" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" t="n">
         <v>12.31620569749018</v>
       </c>
     </row>
@@ -3327,6 +3554,9 @@
         </is>
       </c>
       <c r="J76" t="n">
+        <v>11</v>
+      </c>
+      <c r="K76" t="n">
         <v>12.66141284150133</v>
       </c>
     </row>
@@ -3365,6 +3595,9 @@
         </is>
       </c>
       <c r="J77" t="n">
+        <v>11</v>
+      </c>
+      <c r="K77" t="n">
         <v>13.00449390422686</v>
       </c>
     </row>
@@ -3403,6 +3636,9 @@
         </is>
       </c>
       <c r="J78" t="n">
+        <v>11</v>
+      </c>
+      <c r="K78" t="n">
         <v>9.12738816852228</v>
       </c>
     </row>
@@ -3441,6 +3677,9 @@
         </is>
       </c>
       <c r="J79" t="n">
+        <v>11</v>
+      </c>
+      <c r="K79" t="n">
         <v>8.68658704571123</v>
       </c>
     </row>
@@ -3479,6 +3718,9 @@
         </is>
       </c>
       <c r="J80" t="n">
+        <v>11</v>
+      </c>
+      <c r="K80" t="n">
         <v>8.681894726582</v>
       </c>
     </row>
@@ -3517,6 +3759,9 @@
         </is>
       </c>
       <c r="J81" t="n">
+        <v>11</v>
+      </c>
+      <c r="K81" t="n">
         <v>8.693004759293984</v>
       </c>
     </row>
@@ -3555,6 +3800,9 @@
         </is>
       </c>
       <c r="J82" t="n">
+        <v>11</v>
+      </c>
+      <c r="K82" t="n">
         <v>8.725149125649589</v>
       </c>
     </row>
@@ -3593,6 +3841,9 @@
         </is>
       </c>
       <c r="J83" t="n">
+        <v>11</v>
+      </c>
+      <c r="K83" t="n">
         <v>8.767374629969833</v>
       </c>
     </row>
@@ -3631,6 +3882,9 @@
         </is>
       </c>
       <c r="J84" t="n">
+        <v>11</v>
+      </c>
+      <c r="K84" t="n">
         <v>8.810038227616156</v>
       </c>
     </row>
@@ -3669,6 +3923,9 @@
         </is>
       </c>
       <c r="J85" t="n">
+        <v>11</v>
+      </c>
+      <c r="K85" t="n">
         <v>8.810038227616156</v>
       </c>
     </row>
@@ -3707,6 +3964,9 @@
         </is>
       </c>
       <c r="J86" t="n">
+        <v>11</v>
+      </c>
+      <c r="K86" t="n">
         <v>8.979920966893374</v>
       </c>
     </row>
@@ -3745,6 +4005,9 @@
         </is>
       </c>
       <c r="J87" t="n">
+        <v>11</v>
+      </c>
+      <c r="K87" t="n">
         <v>9.189485465294592</v>
       </c>
     </row>
@@ -3783,6 +4046,9 @@
         </is>
       </c>
       <c r="J88" t="n">
+        <v>11</v>
+      </c>
+      <c r="K88" t="n">
         <v>9.20061339885968</v>
       </c>
     </row>
@@ -3821,6 +4087,9 @@
         </is>
       </c>
       <c r="J89" t="n">
+        <v>11</v>
+      </c>
+      <c r="K89" t="n">
         <v>9.385776211530537</v>
       </c>
     </row>
@@ -3859,6 +4128,9 @@
         </is>
       </c>
       <c r="J90" t="n">
+        <v>11</v>
+      </c>
+      <c r="K90" t="n">
         <v>9.385776211530537</v>
       </c>
     </row>
@@ -3897,6 +4169,9 @@
         </is>
       </c>
       <c r="J91" t="n">
+        <v>11</v>
+      </c>
+      <c r="K91" t="n">
         <v>9.594901878548837</v>
       </c>
     </row>
@@ -3935,6 +4210,9 @@
         </is>
       </c>
       <c r="J92" t="n">
+        <v>11</v>
+      </c>
+      <c r="K92" t="n">
         <v>9.711631620980414</v>
       </c>
     </row>
@@ -3973,6 +4251,9 @@
         </is>
       </c>
       <c r="J93" t="n">
+        <v>11</v>
+      </c>
+      <c r="K93" t="n">
         <v>9.812453513515775</v>
       </c>
     </row>
@@ -4011,6 +4292,9 @@
         </is>
       </c>
       <c r="J94" t="n">
+        <v>11</v>
+      </c>
+      <c r="K94" t="n">
         <v>9.974311185902952</v>
       </c>
     </row>
@@ -4049,6 +4333,9 @@
         </is>
       </c>
       <c r="J95" t="n">
+        <v>11</v>
+      </c>
+      <c r="K95" t="n">
         <v>10.02205133288883</v>
       </c>
     </row>
@@ -4087,6 +4374,9 @@
         </is>
       </c>
       <c r="J96" t="n">
+        <v>11</v>
+      </c>
+      <c r="K96" t="n">
         <v>10.28025187896138</v>
       </c>
     </row>
@@ -4125,6 +4415,9 @@
         </is>
       </c>
       <c r="J97" t="n">
+        <v>11</v>
+      </c>
+      <c r="K97" t="n">
         <v>10.38618001855317</v>
       </c>
     </row>
@@ -4163,6 +4456,9 @@
         </is>
       </c>
       <c r="J98" t="n">
+        <v>11</v>
+      </c>
+      <c r="K98" t="n">
         <v>10.44776992585482</v>
       </c>
     </row>
@@ -4201,6 +4497,9 @@
         </is>
       </c>
       <c r="J99" t="n">
+        <v>11</v>
+      </c>
+      <c r="K99" t="n">
         <v>10.55026105538567</v>
       </c>
     </row>
@@ -4239,6 +4538,9 @@
         </is>
       </c>
       <c r="J100" t="n">
+        <v>11</v>
+      </c>
+      <c r="K100" t="n">
         <v>10.55640596549939</v>
       </c>
     </row>
@@ -4277,6 +4579,9 @@
         </is>
       </c>
       <c r="J101" t="n">
+        <v>11</v>
+      </c>
+      <c r="K101" t="n">
         <v>10.52219052114853</v>
       </c>
     </row>
@@ -4315,6 +4620,9 @@
         </is>
       </c>
       <c r="J102" t="n">
+        <v>11</v>
+      </c>
+      <c r="K102" t="n">
         <v>10.4808184702455</v>
       </c>
     </row>
@@ -4353,6 +4661,9 @@
         </is>
       </c>
       <c r="J103" t="n">
+        <v>11</v>
+      </c>
+      <c r="K103" t="n">
         <v>10.45075109019776</v>
       </c>
     </row>
@@ -4391,6 +4702,9 @@
         </is>
       </c>
       <c r="J104" t="n">
+        <v>11</v>
+      </c>
+      <c r="K104" t="n">
         <v>10.42180488538178</v>
       </c>
     </row>
@@ -4429,6 +4743,9 @@
         </is>
       </c>
       <c r="J105" t="n">
+        <v>11</v>
+      </c>
+      <c r="K105" t="n">
         <v>10.41806567842505</v>
       </c>
     </row>
@@ -4467,6 +4784,9 @@
         </is>
       </c>
       <c r="J106" t="n">
+        <v>11</v>
+      </c>
+      <c r="K106" t="n">
         <v>10.3885771773526</v>
       </c>
     </row>
@@ -4505,6 +4825,9 @@
         </is>
       </c>
       <c r="J107" t="n">
+        <v>11</v>
+      </c>
+      <c r="K107" t="n">
         <v>10.45060969889723</v>
       </c>
     </row>
@@ -4543,6 +4866,9 @@
         </is>
       </c>
       <c r="J108" t="n">
+        <v>11</v>
+      </c>
+      <c r="K108" t="n">
         <v>10.50364497429563</v>
       </c>
     </row>
@@ -4581,6 +4907,9 @@
         </is>
       </c>
       <c r="J109" t="n">
+        <v>11</v>
+      </c>
+      <c r="K109" t="n">
         <v>10.81779559383239</v>
       </c>
     </row>
@@ -4619,6 +4948,9 @@
         </is>
       </c>
       <c r="J110" t="n">
+        <v>11</v>
+      </c>
+      <c r="K110" t="n">
         <v>10.9357231825844</v>
       </c>
     </row>
@@ -4657,6 +4989,9 @@
         </is>
       </c>
       <c r="J111" t="n">
+        <v>11</v>
+      </c>
+      <c r="K111" t="n">
         <v>11.55281843846564</v>
       </c>
     </row>
@@ -4695,6 +5030,9 @@
         </is>
       </c>
       <c r="J112" t="n">
+        <v>11</v>
+      </c>
+      <c r="K112" t="n">
         <v>13.24905110056308</v>
       </c>
     </row>
@@ -4733,6 +5071,9 @@
         </is>
       </c>
       <c r="J113" t="n">
+        <v>11</v>
+      </c>
+      <c r="K113" t="n">
         <v>13.24905110056308</v>
       </c>
     </row>
@@ -4771,6 +5112,9 @@
         </is>
       </c>
       <c r="J114" t="n">
+        <v>11</v>
+      </c>
+      <c r="K114" t="n">
         <v>13.96546733948439</v>
       </c>
     </row>
@@ -4809,6 +5153,9 @@
         </is>
       </c>
       <c r="J115" t="n">
+        <v>11</v>
+      </c>
+      <c r="K115" t="n">
         <v>14.09499060277884</v>
       </c>
     </row>
@@ -4847,6 +5194,9 @@
         </is>
       </c>
       <c r="J116" t="n">
+        <v>11</v>
+      </c>
+      <c r="K116" t="n">
         <v>14.10231971947695</v>
       </c>
     </row>
@@ -4885,6 +5235,9 @@
         </is>
       </c>
       <c r="J117" t="n">
+        <v>11</v>
+      </c>
+      <c r="K117" t="n">
         <v>13.32115312121745</v>
       </c>
     </row>
@@ -4923,6 +5276,9 @@
         </is>
       </c>
       <c r="J118" t="n">
+        <v>11</v>
+      </c>
+      <c r="K118" t="n">
         <v>12.18673597949732</v>
       </c>
     </row>
@@ -4961,6 +5317,9 @@
         </is>
       </c>
       <c r="J119" t="n">
+        <v>11</v>
+      </c>
+      <c r="K119" t="n">
         <v>11.61520007469289</v>
       </c>
     </row>
@@ -4999,6 +5358,9 @@
         </is>
       </c>
       <c r="J120" t="n">
+        <v>11</v>
+      </c>
+      <c r="K120" t="n">
         <v>10.7717653162068</v>
       </c>
     </row>
@@ -5037,6 +5399,9 @@
         </is>
       </c>
       <c r="J121" t="n">
+        <v>11</v>
+      </c>
+      <c r="K121" t="n">
         <v>10.62118096941062</v>
       </c>
     </row>
@@ -5075,6 +5440,9 @@
         </is>
       </c>
       <c r="J122" t="n">
+        <v>11</v>
+      </c>
+      <c r="K122" t="n">
         <v>10.62118096941062</v>
       </c>
     </row>
@@ -5113,6 +5481,9 @@
         </is>
       </c>
       <c r="J123" t="n">
+        <v>11</v>
+      </c>
+      <c r="K123" t="n">
         <v>10.45511537631013</v>
       </c>
     </row>
@@ -5151,6 +5522,9 @@
         </is>
       </c>
       <c r="J124" t="n">
+        <v>11</v>
+      </c>
+      <c r="K124" t="n">
         <v>10.44611547119964</v>
       </c>
     </row>
@@ -5189,6 +5563,9 @@
         </is>
       </c>
       <c r="J125" t="n">
+        <v>11</v>
+      </c>
+      <c r="K125" t="n">
         <v>10.40516927885814</v>
       </c>
     </row>
@@ -5227,6 +5604,9 @@
         </is>
       </c>
       <c r="J126" t="n">
+        <v>11</v>
+      </c>
+      <c r="K126" t="n">
         <v>10.15234578612369</v>
       </c>
     </row>
@@ -5265,6 +5645,9 @@
         </is>
       </c>
       <c r="J127" t="n">
+        <v>11</v>
+      </c>
+      <c r="K127" t="n">
         <v>10.12854983494127</v>
       </c>
     </row>
@@ -5303,6 +5686,9 @@
         </is>
       </c>
       <c r="J128" t="n">
+        <v>11</v>
+      </c>
+      <c r="K128" t="n">
         <v>10.13429438631349</v>
       </c>
     </row>
@@ -5341,6 +5727,9 @@
         </is>
       </c>
       <c r="J129" t="n">
+        <v>11</v>
+      </c>
+      <c r="K129" t="n">
         <v>10.16702268282531</v>
       </c>
     </row>
@@ -5379,6 +5768,9 @@
         </is>
       </c>
       <c r="J130" t="n">
+        <v>11</v>
+      </c>
+      <c r="K130" t="n">
         <v>10.19850456500321</v>
       </c>
     </row>
@@ -5417,6 +5809,9 @@
         </is>
       </c>
       <c r="J131" t="n">
+        <v>11</v>
+      </c>
+      <c r="K131" t="n">
         <v>10.15988699682155</v>
       </c>
     </row>
@@ -5455,6 +5850,9 @@
         </is>
       </c>
       <c r="J132" t="n">
+        <v>11</v>
+      </c>
+      <c r="K132" t="n">
         <v>10.15045600603868</v>
       </c>
     </row>
@@ -5493,6 +5891,9 @@
         </is>
       </c>
       <c r="J133" t="n">
+        <v>11</v>
+      </c>
+      <c r="K133" t="n">
         <v>10.15045600603868</v>
       </c>
     </row>
@@ -5531,6 +5932,9 @@
         </is>
       </c>
       <c r="J134" t="n">
+        <v>11</v>
+      </c>
+      <c r="K134" t="n">
         <v>9.889113576235221</v>
       </c>
     </row>
@@ -5569,6 +5973,9 @@
         </is>
       </c>
       <c r="J135" t="n">
+        <v>11</v>
+      </c>
+      <c r="K135" t="n">
         <v>9.889113576235221</v>
       </c>
     </row>
@@ -5607,6 +6014,9 @@
         </is>
       </c>
       <c r="J136" t="n">
+        <v>11</v>
+      </c>
+      <c r="K136" t="n">
         <v>9.503480022823256</v>
       </c>
     </row>
@@ -5645,6 +6055,9 @@
         </is>
       </c>
       <c r="J137" t="n">
+        <v>11</v>
+      </c>
+      <c r="K137" t="n">
         <v>9.503480022823256</v>
       </c>
     </row>
@@ -5683,6 +6096,9 @@
         </is>
       </c>
       <c r="J138" t="n">
+        <v>11</v>
+      </c>
+      <c r="K138" t="n">
         <v>9.273302827189962</v>
       </c>
     </row>
@@ -5721,6 +6137,9 @@
         </is>
       </c>
       <c r="J139" t="n">
+        <v>11</v>
+      </c>
+      <c r="K139" t="n">
         <v>9.323353732391949</v>
       </c>
     </row>
@@ -5759,6 +6178,9 @@
         </is>
       </c>
       <c r="J140" t="n">
+        <v>11</v>
+      </c>
+      <c r="K140" t="n">
         <v>9.538199059605576</v>
       </c>
     </row>
@@ -5797,6 +6219,9 @@
         </is>
       </c>
       <c r="J141" t="n">
+        <v>11</v>
+      </c>
+      <c r="K141" t="n">
         <v>9.595159351550077</v>
       </c>
     </row>
@@ -5835,6 +6260,9 @@
         </is>
       </c>
       <c r="J142" t="n">
+        <v>11</v>
+      </c>
+      <c r="K142" t="n">
         <v>9.640228187381412</v>
       </c>
     </row>
@@ -5873,6 +6301,9 @@
         </is>
       </c>
       <c r="J143" t="n">
+        <v>11</v>
+      </c>
+      <c r="K143" t="n">
         <v>9.67585678642285</v>
       </c>
     </row>
@@ -5911,6 +6342,9 @@
         </is>
       </c>
       <c r="J144" t="n">
+        <v>11</v>
+      </c>
+      <c r="K144" t="n">
         <v>9.67585678642285</v>
       </c>
     </row>
@@ -5949,6 +6383,9 @@
         </is>
       </c>
       <c r="J145" t="n">
+        <v>11</v>
+      </c>
+      <c r="K145" t="n">
         <v>9.644544295013892</v>
       </c>
     </row>
@@ -5987,6 +6424,9 @@
         </is>
       </c>
       <c r="J146" t="n">
+        <v>11</v>
+      </c>
+      <c r="K146" t="n">
         <v>9.575393468358264</v>
       </c>
     </row>
@@ -6025,6 +6465,9 @@
         </is>
       </c>
       <c r="J147" t="n">
+        <v>11</v>
+      </c>
+      <c r="K147" t="n">
         <v>9.509165247009472</v>
       </c>
     </row>
@@ -6063,6 +6506,9 @@
         </is>
       </c>
       <c r="J148" t="n">
+        <v>11</v>
+      </c>
+      <c r="K148" t="n">
         <v>9.186890150588898</v>
       </c>
     </row>
@@ -6101,6 +6547,9 @@
         </is>
       </c>
       <c r="J149" t="n">
+        <v>11</v>
+      </c>
+      <c r="K149" t="n">
         <v>8.892310645809815</v>
       </c>
     </row>
@@ -6139,6 +6588,9 @@
         </is>
       </c>
       <c r="J150" t="n">
+        <v>11</v>
+      </c>
+      <c r="K150" t="n">
         <v>8.798285875284799</v>
       </c>
     </row>
@@ -6177,6 +6629,9 @@
         </is>
       </c>
       <c r="J151" t="n">
+        <v>11</v>
+      </c>
+      <c r="K151" t="n">
         <v>8.875333945274798</v>
       </c>
     </row>
@@ -6215,6 +6670,9 @@
         </is>
       </c>
       <c r="J152" t="n">
+        <v>11</v>
+      </c>
+      <c r="K152" t="n">
         <v>8.916837319105506</v>
       </c>
     </row>
@@ -6253,6 +6711,9 @@
         </is>
       </c>
       <c r="J153" t="n">
+        <v>11</v>
+      </c>
+      <c r="K153" t="n">
         <v>9.076727962887233</v>
       </c>
     </row>
@@ -6291,6 +6752,9 @@
         </is>
       </c>
       <c r="J154" t="n">
+        <v>11</v>
+      </c>
+      <c r="K154" t="n">
         <v>9.266264516167034</v>
       </c>
     </row>
@@ -6329,6 +6793,9 @@
         </is>
       </c>
       <c r="J155" t="n">
+        <v>11</v>
+      </c>
+      <c r="K155" t="n">
         <v>9.383051777516972</v>
       </c>
     </row>
@@ -6367,6 +6834,9 @@
         </is>
       </c>
       <c r="J156" t="n">
+        <v>11</v>
+      </c>
+      <c r="K156" t="n">
         <v>9.383051777516972</v>
       </c>
     </row>
@@ -6405,6 +6875,9 @@
         </is>
       </c>
       <c r="J157" t="n">
+        <v>11</v>
+      </c>
+      <c r="K157" t="n">
         <v>9.460674517214896</v>
       </c>
     </row>
@@ -6443,6 +6916,9 @@
         </is>
       </c>
       <c r="J158" t="n">
+        <v>11</v>
+      </c>
+      <c r="K158" t="n">
         <v>9.460674517214896</v>
       </c>
     </row>
@@ -6481,6 +6957,9 @@
         </is>
       </c>
       <c r="J159" t="n">
+        <v>11</v>
+      </c>
+      <c r="K159" t="n">
         <v>9.459995832832561</v>
       </c>
     </row>
@@ -6519,6 +6998,9 @@
         </is>
       </c>
       <c r="J160" t="n">
+        <v>11</v>
+      </c>
+      <c r="K160" t="n">
         <v>9.459995832832561</v>
       </c>
     </row>
@@ -6557,6 +7039,9 @@
         </is>
       </c>
       <c r="J161" t="n">
+        <v>11</v>
+      </c>
+      <c r="K161" t="n">
         <v>9.442058385983874</v>
       </c>
     </row>
@@ -6595,6 +7080,9 @@
         </is>
       </c>
       <c r="J162" t="n">
+        <v>11</v>
+      </c>
+      <c r="K162" t="n">
         <v>9.44635359893042</v>
       </c>
     </row>
@@ -6633,6 +7121,9 @@
         </is>
       </c>
       <c r="J163" t="n">
+        <v>11</v>
+      </c>
+      <c r="K163" t="n">
         <v>9.44078455669402</v>
       </c>
     </row>
@@ -6671,6 +7162,9 @@
         </is>
       </c>
       <c r="J164" t="n">
+        <v>11</v>
+      </c>
+      <c r="K164" t="n">
         <v>9.44078455669402</v>
       </c>
     </row>
@@ -6709,6 +7203,9 @@
         </is>
       </c>
       <c r="J165" t="n">
+        <v>11</v>
+      </c>
+      <c r="K165" t="n">
         <v>9.436919149557639</v>
       </c>
     </row>
@@ -6747,6 +7244,9 @@
         </is>
       </c>
       <c r="J166" t="n">
+        <v>11</v>
+      </c>
+      <c r="K166" t="n">
         <v>9.471086390640769</v>
       </c>
     </row>
@@ -6785,6 +7285,9 @@
         </is>
       </c>
       <c r="J167" t="n">
+        <v>11</v>
+      </c>
+      <c r="K167" t="n">
         <v>9.471086390640769</v>
       </c>
     </row>
@@ -6823,6 +7326,9 @@
         </is>
       </c>
       <c r="J168" t="n">
+        <v>11</v>
+      </c>
+      <c r="K168" t="n">
         <v>9.471086390640769</v>
       </c>
     </row>
@@ -6861,6 +7367,9 @@
         </is>
       </c>
       <c r="J169" t="n">
+        <v>11</v>
+      </c>
+      <c r="K169" t="n">
         <v>9.558331869346324</v>
       </c>
     </row>
@@ -6899,6 +7408,9 @@
         </is>
       </c>
       <c r="J170" t="n">
+        <v>13</v>
+      </c>
+      <c r="K170" t="n">
         <v>10.55331911901448</v>
       </c>
     </row>
@@ -6937,6 +7449,9 @@
         </is>
       </c>
       <c r="J171" t="n">
+        <v>13</v>
+      </c>
+      <c r="K171" t="n">
         <v>10.97574274908715</v>
       </c>
     </row>
@@ -6975,6 +7490,9 @@
         </is>
       </c>
       <c r="J172" t="n">
+        <v>13</v>
+      </c>
+      <c r="K172" t="n">
         <v>12.49691388284474</v>
       </c>
     </row>
@@ -7013,6 +7531,9 @@
         </is>
       </c>
       <c r="J173" t="n">
+        <v>13</v>
+      </c>
+      <c r="K173" t="n">
         <v>13.23294049977152</v>
       </c>
     </row>
@@ -7051,6 +7572,9 @@
         </is>
       </c>
       <c r="J174" t="n">
+        <v>13</v>
+      </c>
+      <c r="K174" t="n">
         <v>14.14162708229524</v>
       </c>
     </row>
@@ -7089,6 +7613,9 @@
         </is>
       </c>
       <c r="J175" t="n">
+        <v>13</v>
+      </c>
+      <c r="K175" t="n">
         <v>15.08727790142</v>
       </c>
     </row>
@@ -7127,6 +7654,9 @@
         </is>
       </c>
       <c r="J176" t="n">
+        <v>13</v>
+      </c>
+      <c r="K176" t="n">
         <v>15.85430464949789</v>
       </c>
     </row>
@@ -7165,6 +7695,9 @@
         </is>
       </c>
       <c r="J177" t="n">
+        <v>13</v>
+      </c>
+      <c r="K177" t="n">
         <v>16.05225719177724</v>
       </c>
     </row>
@@ -7203,6 +7736,9 @@
         </is>
       </c>
       <c r="J178" t="n">
+        <v>13</v>
+      </c>
+      <c r="K178" t="n">
         <v>16.05225719177724</v>
       </c>
     </row>
@@ -7241,6 +7777,9 @@
         </is>
       </c>
       <c r="J179" t="n">
+        <v>13</v>
+      </c>
+      <c r="K179" t="n">
         <v>15.41681884273828</v>
       </c>
     </row>
@@ -7279,6 +7818,9 @@
         </is>
       </c>
       <c r="J180" t="n">
+        <v>13</v>
+      </c>
+      <c r="K180" t="n">
         <v>14.85223332821751</v>
       </c>
     </row>
@@ -7317,6 +7859,9 @@
         </is>
       </c>
       <c r="J181" t="n">
+        <v>13</v>
+      </c>
+      <c r="K181" t="n">
         <v>14.85223332821751</v>
       </c>
     </row>
@@ -7355,6 +7900,9 @@
         </is>
       </c>
       <c r="J182" t="n">
+        <v>13</v>
+      </c>
+      <c r="K182" t="n">
         <v>13.87028048897389</v>
       </c>
     </row>
@@ -7393,6 +7941,9 @@
         </is>
       </c>
       <c r="J183" t="n">
+        <v>13</v>
+      </c>
+      <c r="K183" t="n">
         <v>13.48909493485402</v>
       </c>
     </row>
@@ -7431,6 +7982,9 @@
         </is>
       </c>
       <c r="J184" t="n">
+        <v>13</v>
+      </c>
+      <c r="K184" t="n">
         <v>13.48909493485402</v>
       </c>
     </row>
@@ -7469,6 +8023,9 @@
         </is>
       </c>
       <c r="J185" t="n">
+        <v>13</v>
+      </c>
+      <c r="K185" t="n">
         <v>13.09392521274405</v>
       </c>
     </row>
@@ -7507,6 +8064,9 @@
         </is>
       </c>
       <c r="J186" t="n">
+        <v>13</v>
+      </c>
+      <c r="K186" t="n">
         <v>12.83928370268094</v>
       </c>
     </row>
@@ -7545,6 +8105,9 @@
         </is>
       </c>
       <c r="J187" t="n">
+        <v>13</v>
+      </c>
+      <c r="K187" t="n">
         <v>12.75220267877187</v>
       </c>
     </row>
@@ -7583,6 +8146,9 @@
         </is>
       </c>
       <c r="J188" t="n">
+        <v>13</v>
+      </c>
+      <c r="K188" t="n">
         <v>12.65161912803199</v>
       </c>
     </row>
@@ -7621,6 +8187,9 @@
         </is>
       </c>
       <c r="J189" t="n">
+        <v>13</v>
+      </c>
+      <c r="K189" t="n">
         <v>12.38198982180875</v>
       </c>
     </row>
@@ -7659,6 +8228,9 @@
         </is>
       </c>
       <c r="J190" t="n">
+        <v>13</v>
+      </c>
+      <c r="K190" t="n">
         <v>11.8071681535344</v>
       </c>
     </row>
@@ -7697,6 +8269,9 @@
         </is>
       </c>
       <c r="J191" t="n">
+        <v>13</v>
+      </c>
+      <c r="K191" t="n">
         <v>2.375343852709965</v>
       </c>
     </row>
@@ -7735,6 +8310,9 @@
         </is>
       </c>
       <c r="J192" t="n">
+        <v>13</v>
+      </c>
+      <c r="K192" t="n">
         <v>2.375343852709965</v>
       </c>
     </row>
@@ -7773,6 +8351,9 @@
         </is>
       </c>
       <c r="J193" t="n">
+        <v>13</v>
+      </c>
+      <c r="K193" t="n">
         <v>2.403093697979613</v>
       </c>
     </row>
@@ -7811,6 +8392,9 @@
         </is>
       </c>
       <c r="J194" t="n">
+        <v>13</v>
+      </c>
+      <c r="K194" t="n">
         <v>2.565977898371402</v>
       </c>
     </row>
@@ -7849,6 +8433,9 @@
         </is>
       </c>
       <c r="J195" t="n">
+        <v>13</v>
+      </c>
+      <c r="K195" t="n">
         <v>11.85212475762777</v>
       </c>
     </row>
@@ -7887,6 +8474,9 @@
         </is>
       </c>
       <c r="J196" t="n">
+        <v>13</v>
+      </c>
+      <c r="K196" t="n">
         <v>11.85212475762777</v>
       </c>
     </row>
@@ -7925,6 +8515,9 @@
         </is>
       </c>
       <c r="J197" t="n">
+        <v>13</v>
+      </c>
+      <c r="K197" t="n">
         <v>11.85212475762777</v>
       </c>
     </row>
@@ -7963,6 +8556,9 @@
         </is>
       </c>
       <c r="J198" t="n">
+        <v>13</v>
+      </c>
+      <c r="K198" t="n">
         <v>12.765658678647</v>
       </c>
     </row>
@@ -8001,6 +8597,9 @@
         </is>
       </c>
       <c r="J199" t="n">
+        <v>13</v>
+      </c>
+      <c r="K199" t="n">
         <v>13.38283727671386</v>
       </c>
     </row>
@@ -8039,6 +8638,9 @@
         </is>
       </c>
       <c r="J200" t="n">
+        <v>13</v>
+      </c>
+      <c r="K200" t="n">
         <v>13.38283727671386</v>
       </c>
     </row>
@@ -8077,6 +8679,9 @@
         </is>
       </c>
       <c r="J201" t="n">
+        <v>13</v>
+      </c>
+      <c r="K201" t="n">
         <v>13.38283727671386</v>
       </c>
     </row>
@@ -8115,6 +8720,9 @@
         </is>
       </c>
       <c r="J202" t="n">
+        <v>13</v>
+      </c>
+      <c r="K202" t="n">
         <v>13.38283727671386</v>
       </c>
     </row>
@@ -8153,6 +8761,9 @@
         </is>
       </c>
       <c r="J203" t="n">
+        <v>13</v>
+      </c>
+      <c r="K203" t="n">
         <v>13.38283727671386</v>
       </c>
     </row>
@@ -8191,6 +8802,9 @@
         </is>
       </c>
       <c r="J204" t="n">
+        <v>13</v>
+      </c>
+      <c r="K204" t="n">
         <v>11.841804383611</v>
       </c>
     </row>
@@ -8229,6 +8843,9 @@
         </is>
       </c>
       <c r="J205" t="n">
+        <v>13</v>
+      </c>
+      <c r="K205" t="n">
         <v>11.841804383611</v>
       </c>
     </row>
@@ -8267,6 +8884,9 @@
         </is>
       </c>
       <c r="J206" t="n">
+        <v>13</v>
+      </c>
+      <c r="K206" t="n">
         <v>11.841804383611</v>
       </c>
     </row>
@@ -8305,6 +8925,9 @@
         </is>
       </c>
       <c r="J207" t="n">
+        <v>13</v>
+      </c>
+      <c r="K207" t="n">
         <v>11.841804383611</v>
       </c>
     </row>
@@ -8343,6 +8966,9 @@
         </is>
       </c>
       <c r="J208" t="n">
+        <v>13</v>
+      </c>
+      <c r="K208" t="n">
         <v>11.5581609664542</v>
       </c>
     </row>
@@ -8381,6 +9007,9 @@
         </is>
       </c>
       <c r="J209" t="n">
+        <v>13</v>
+      </c>
+      <c r="K209" t="n">
         <v>2.182238964742554</v>
       </c>
     </row>
@@ -8419,6 +9048,9 @@
         </is>
       </c>
       <c r="J210" t="n">
+        <v>13</v>
+      </c>
+      <c r="K210" t="n">
         <v>1.908400853213792</v>
       </c>
     </row>
@@ -8457,6 +9089,9 @@
         </is>
       </c>
       <c r="J211" t="n">
+        <v>13</v>
+      </c>
+      <c r="K211" t="n">
         <v>1.928104875567422</v>
       </c>
     </row>
@@ -8495,6 +9130,9 @@
         </is>
       </c>
       <c r="J212" t="n">
+        <v>13</v>
+      </c>
+      <c r="K212" t="n">
         <v>1.928104875567422</v>
       </c>
     </row>
@@ -8533,6 +9171,9 @@
         </is>
       </c>
       <c r="J213" t="n">
+        <v>13</v>
+      </c>
+      <c r="K213" t="n">
         <v>1.946527496520316</v>
       </c>
     </row>
@@ -8571,6 +9212,9 @@
         </is>
       </c>
       <c r="J214" t="n">
+        <v>13</v>
+      </c>
+      <c r="K214" t="n">
         <v>2.000068265384438</v>
       </c>
     </row>
@@ -8609,6 +9253,9 @@
         </is>
       </c>
       <c r="J215" t="n">
+        <v>13</v>
+      </c>
+      <c r="K215" t="n">
         <v>2.000068265384438</v>
       </c>
     </row>
@@ -8647,6 +9294,9 @@
         </is>
       </c>
       <c r="J216" t="n">
+        <v>13</v>
+      </c>
+      <c r="K216" t="n">
         <v>2.228818630840926</v>
       </c>
     </row>
@@ -8685,6 +9335,9 @@
         </is>
       </c>
       <c r="J217" t="n">
+        <v>13</v>
+      </c>
+      <c r="K217" t="n">
         <v>2.228818630840926</v>
       </c>
     </row>
@@ -8723,6 +9376,9 @@
         </is>
       </c>
       <c r="J218" t="n">
+        <v>13</v>
+      </c>
+      <c r="K218" t="n">
         <v>2.501604773914607</v>
       </c>
     </row>
@@ -8761,6 +9417,9 @@
         </is>
       </c>
       <c r="J219" t="n">
+        <v>13</v>
+      </c>
+      <c r="K219" t="n">
         <v>2.501604773914607</v>
       </c>
     </row>
@@ -8799,6 +9458,9 @@
         </is>
       </c>
       <c r="J220" t="n">
+        <v>13</v>
+      </c>
+      <c r="K220" t="n">
         <v>2.501604773914607</v>
       </c>
     </row>
@@ -8837,6 +9499,9 @@
         </is>
       </c>
       <c r="J221" t="n">
+        <v>13</v>
+      </c>
+      <c r="K221" t="n">
         <v>2.864888144822098</v>
       </c>
     </row>
@@ -8875,6 +9540,9 @@
         </is>
       </c>
       <c r="J222" t="n">
+        <v>13</v>
+      </c>
+      <c r="K222" t="n">
         <v>3.094640752480634</v>
       </c>
     </row>
@@ -8913,6 +9581,9 @@
         </is>
       </c>
       <c r="J223" t="n">
+        <v>13</v>
+      </c>
+      <c r="K223" t="n">
         <v>3.272130625156524</v>
       </c>
     </row>
@@ -8951,6 +9622,9 @@
         </is>
       </c>
       <c r="J224" t="n">
+        <v>13</v>
+      </c>
+      <c r="K224" t="n">
         <v>3.293214151886771</v>
       </c>
     </row>
@@ -8989,6 +9663,9 @@
         </is>
       </c>
       <c r="J225" t="n">
+        <v>13</v>
+      </c>
+      <c r="K225" t="n">
         <v>3.293214151886771</v>
       </c>
     </row>
@@ -9027,6 +9704,9 @@
         </is>
       </c>
       <c r="J226" t="n">
+        <v>13</v>
+      </c>
+      <c r="K226" t="n">
         <v>3.239899719607355</v>
       </c>
     </row>
@@ -9065,6 +9745,9 @@
         </is>
       </c>
       <c r="J227" t="n">
+        <v>13</v>
+      </c>
+      <c r="K227" t="n">
         <v>3.19237736532465</v>
       </c>
     </row>
@@ -9103,6 +9786,9 @@
         </is>
       </c>
       <c r="J228" t="n">
+        <v>13</v>
+      </c>
+      <c r="K228" t="n">
         <v>3.133882975962623</v>
       </c>
     </row>
@@ -9141,6 +9827,9 @@
         </is>
       </c>
       <c r="J229" t="n">
+        <v>13</v>
+      </c>
+      <c r="K229" t="n">
         <v>3.133882975962623</v>
       </c>
     </row>
@@ -9179,6 +9868,9 @@
         </is>
       </c>
       <c r="J230" t="n">
+        <v>13</v>
+      </c>
+      <c r="K230" t="n">
         <v>3.044829795797425</v>
       </c>
     </row>
@@ -9217,6 +9909,9 @@
         </is>
       </c>
       <c r="J231" t="n">
+        <v>13</v>
+      </c>
+      <c r="K231" t="n">
         <v>2.899990053129708</v>
       </c>
     </row>
@@ -9255,6 +9950,9 @@
         </is>
       </c>
       <c r="J232" t="n">
+        <v>13</v>
+      </c>
+      <c r="K232" t="n">
         <v>2.899990053129708</v>
       </c>
     </row>
@@ -9293,6 +9991,9 @@
         </is>
       </c>
       <c r="J233" t="n">
+        <v>13</v>
+      </c>
+      <c r="K233" t="n">
         <v>2.733413616260812</v>
       </c>
     </row>
@@ -9331,6 +10032,9 @@
         </is>
       </c>
       <c r="J234" t="n">
+        <v>13</v>
+      </c>
+      <c r="K234" t="n">
         <v>2.733413616260812</v>
       </c>
     </row>
@@ -9369,6 +10073,9 @@
         </is>
       </c>
       <c r="J235" t="n">
+        <v>13</v>
+      </c>
+      <c r="K235" t="n">
         <v>2.423390682561244</v>
       </c>
     </row>
@@ -9407,6 +10114,9 @@
         </is>
       </c>
       <c r="J236" t="n">
+        <v>13</v>
+      </c>
+      <c r="K236" t="n">
         <v>2.423390682561244</v>
       </c>
     </row>
@@ -9445,6 +10155,9 @@
         </is>
       </c>
       <c r="J237" t="n">
+        <v>13</v>
+      </c>
+      <c r="K237" t="n">
         <v>2.423390682561244</v>
       </c>
     </row>
@@ -9483,6 +10196,9 @@
         </is>
       </c>
       <c r="J238" t="n">
+        <v>13</v>
+      </c>
+      <c r="K238" t="n">
         <v>2.271389242176518</v>
       </c>
     </row>
@@ -9521,6 +10237,9 @@
         </is>
       </c>
       <c r="J239" t="n">
+        <v>13</v>
+      </c>
+      <c r="K239" t="n">
         <v>2.02252475559434</v>
       </c>
     </row>
@@ -9559,6 +10278,9 @@
         </is>
       </c>
       <c r="J240" t="n">
+        <v>13</v>
+      </c>
+      <c r="K240" t="n">
         <v>1.960420584899899</v>
       </c>
     </row>
@@ -9597,6 +10319,9 @@
         </is>
       </c>
       <c r="J241" t="n">
+        <v>13</v>
+      </c>
+      <c r="K241" t="n">
         <v>1.922084617288877</v>
       </c>
     </row>
@@ -9635,6 +10360,9 @@
         </is>
       </c>
       <c r="J242" t="n">
+        <v>13</v>
+      </c>
+      <c r="K242" t="n">
         <v>1.922084617288877</v>
       </c>
     </row>
@@ -9673,6 +10401,9 @@
         </is>
       </c>
       <c r="J243" t="n">
+        <v>13</v>
+      </c>
+      <c r="K243" t="n">
         <v>1.835052498104472</v>
       </c>
     </row>
@@ -9711,6 +10442,9 @@
         </is>
       </c>
       <c r="J244" t="n">
+        <v>13</v>
+      </c>
+      <c r="K244" t="n">
         <v>1.781390400504812</v>
       </c>
     </row>
@@ -9749,6 +10483,9 @@
         </is>
       </c>
       <c r="J245" t="n">
+        <v>13</v>
+      </c>
+      <c r="K245" t="n">
         <v>1.829442920342406</v>
       </c>
     </row>
@@ -9787,6 +10524,9 @@
         </is>
       </c>
       <c r="J246" t="n">
+        <v>13</v>
+      </c>
+      <c r="K246" t="n">
         <v>1.829442920342406</v>
       </c>
     </row>
@@ -9825,6 +10565,9 @@
         </is>
       </c>
       <c r="J247" t="n">
+        <v>13</v>
+      </c>
+      <c r="K247" t="n">
         <v>1.838879048398972</v>
       </c>
     </row>
@@ -9863,6 +10606,9 @@
         </is>
       </c>
       <c r="J248" t="n">
+        <v>13</v>
+      </c>
+      <c r="K248" t="n">
         <v>1.862269297693542</v>
       </c>
     </row>
@@ -9901,6 +10647,9 @@
         </is>
       </c>
       <c r="J249" t="n">
+        <v>13</v>
+      </c>
+      <c r="K249" t="n">
         <v>1.862269297693542</v>
       </c>
     </row>
@@ -9939,6 +10688,9 @@
         </is>
       </c>
       <c r="J250" t="n">
+        <v>13</v>
+      </c>
+      <c r="K250" t="n">
         <v>1.992272159991618</v>
       </c>
     </row>
@@ -9977,6 +10729,9 @@
         </is>
       </c>
       <c r="J251" t="n">
+        <v>13</v>
+      </c>
+      <c r="K251" t="n">
         <v>2.006304273811092</v>
       </c>
     </row>
@@ -10015,6 +10770,9 @@
         </is>
       </c>
       <c r="J252" t="n">
+        <v>13</v>
+      </c>
+      <c r="K252" t="n">
         <v>1.979862095806364</v>
       </c>
     </row>
@@ -10053,6 +10811,9 @@
         </is>
       </c>
       <c r="J253" t="n">
+        <v>13</v>
+      </c>
+      <c r="K253" t="n">
         <v>1.958232963266376</v>
       </c>
     </row>
@@ -10091,6 +10852,9 @@
         </is>
       </c>
       <c r="J254" t="n">
+        <v>13</v>
+      </c>
+      <c r="K254" t="n">
         <v>1.958232963266376</v>
       </c>
     </row>
@@ -10129,6 +10893,9 @@
         </is>
       </c>
       <c r="J255" t="n">
+        <v>13</v>
+      </c>
+      <c r="K255" t="n">
         <v>1.979860907556284</v>
       </c>
     </row>
@@ -10167,6 +10934,9 @@
         </is>
       </c>
       <c r="J256" t="n">
+        <v>13</v>
+      </c>
+      <c r="K256" t="n">
         <v>1.97338395506932</v>
       </c>
     </row>
@@ -10205,6 +10975,9 @@
         </is>
       </c>
       <c r="J257" t="n">
+        <v>13</v>
+      </c>
+      <c r="K257" t="n">
         <v>1.97338395506932</v>
       </c>
     </row>
@@ -10243,6 +11016,9 @@
         </is>
       </c>
       <c r="J258" t="n">
+        <v>13</v>
+      </c>
+      <c r="K258" t="n">
         <v>2.094702487520755</v>
       </c>
     </row>
@@ -10281,6 +11057,9 @@
         </is>
       </c>
       <c r="J259" t="n">
+        <v>13</v>
+      </c>
+      <c r="K259" t="n">
         <v>2.127189173542384</v>
       </c>
     </row>
@@ -10319,6 +11098,9 @@
         </is>
       </c>
       <c r="J260" t="n">
+        <v>13</v>
+      </c>
+      <c r="K260" t="n">
         <v>2.139543690586782</v>
       </c>
     </row>
@@ -10357,6 +11139,9 @@
         </is>
       </c>
       <c r="J261" t="n">
+        <v>13</v>
+      </c>
+      <c r="K261" t="n">
         <v>2.173726475012317</v>
       </c>
     </row>
@@ -10395,6 +11180,9 @@
         </is>
       </c>
       <c r="J262" t="n">
+        <v>13</v>
+      </c>
+      <c r="K262" t="n">
         <v>2.19633243854267</v>
       </c>
     </row>
@@ -10433,6 +11221,9 @@
         </is>
       </c>
       <c r="J263" t="n">
+        <v>13</v>
+      </c>
+      <c r="K263" t="n">
         <v>2.210980517993176</v>
       </c>
     </row>
@@ -10471,6 +11262,9 @@
         </is>
       </c>
       <c r="J264" t="n">
+        <v>13</v>
+      </c>
+      <c r="K264" t="n">
         <v>2.23107155039617</v>
       </c>
     </row>
@@ -10509,6 +11303,9 @@
         </is>
       </c>
       <c r="J265" t="n">
+        <v>13</v>
+      </c>
+      <c r="K265" t="n">
         <v>2.355335196847836</v>
       </c>
     </row>
@@ -10547,6 +11344,9 @@
         </is>
       </c>
       <c r="J266" t="n">
+        <v>13</v>
+      </c>
+      <c r="K266" t="n">
         <v>2.416055884505181</v>
       </c>
     </row>
@@ -10585,6 +11385,9 @@
         </is>
       </c>
       <c r="J267" t="n">
+        <v>13</v>
+      </c>
+      <c r="K267" t="n">
         <v>2.477853451311926</v>
       </c>
     </row>
@@ -10623,6 +11426,9 @@
         </is>
       </c>
       <c r="J268" t="n">
+        <v>13</v>
+      </c>
+      <c r="K268" t="n">
         <v>2.569468355262374</v>
       </c>
     </row>
@@ -10661,6 +11467,9 @@
         </is>
       </c>
       <c r="J269" t="n">
+        <v>13</v>
+      </c>
+      <c r="K269" t="n">
         <v>2.569468355262374</v>
       </c>
     </row>
@@ -10699,6 +11508,9 @@
         </is>
       </c>
       <c r="J270" t="n">
+        <v>13</v>
+      </c>
+      <c r="K270" t="n">
         <v>2.644536362880819</v>
       </c>
     </row>
@@ -10737,6 +11549,9 @@
         </is>
       </c>
       <c r="J271" t="n">
+        <v>13</v>
+      </c>
+      <c r="K271" t="n">
         <v>2.720452503598174</v>
       </c>
     </row>
@@ -10775,6 +11590,9 @@
         </is>
       </c>
       <c r="J272" t="n">
+        <v>13</v>
+      </c>
+      <c r="K272" t="n">
         <v>2.82258817858393</v>
       </c>
     </row>
@@ -10813,6 +11631,9 @@
         </is>
       </c>
       <c r="J273" t="n">
+        <v>13</v>
+      </c>
+      <c r="K273" t="n">
         <v>2.842201598260041</v>
       </c>
     </row>
@@ -10851,6 +11672,9 @@
         </is>
       </c>
       <c r="J274" t="n">
+        <v>13</v>
+      </c>
+      <c r="K274" t="n">
         <v>2.863237632031469</v>
       </c>
     </row>
@@ -10889,6 +11713,9 @@
         </is>
       </c>
       <c r="J275" t="n">
+        <v>13</v>
+      </c>
+      <c r="K275" t="n">
         <v>2.863237632031469</v>
       </c>
     </row>
@@ -10927,6 +11754,9 @@
         </is>
       </c>
       <c r="J276" t="n">
+        <v>13</v>
+      </c>
+      <c r="K276" t="n">
         <v>2.935456735382338</v>
       </c>
     </row>
@@ -10965,6 +11795,9 @@
         </is>
       </c>
       <c r="J277" t="n">
+        <v>13</v>
+      </c>
+      <c r="K277" t="n">
         <v>2.971304894385905</v>
       </c>
     </row>
@@ -11003,6 +11836,9 @@
         </is>
       </c>
       <c r="J278" t="n">
+        <v>13</v>
+      </c>
+      <c r="K278" t="n">
         <v>2.996955943691693</v>
       </c>
     </row>
@@ -11041,6 +11877,9 @@
         </is>
       </c>
       <c r="J279" t="n">
+        <v>13</v>
+      </c>
+      <c r="K279" t="n">
         <v>2.996955943691693</v>
       </c>
     </row>
@@ -11079,6 +11918,9 @@
         </is>
       </c>
       <c r="J280" t="n">
+        <v>13</v>
+      </c>
+      <c r="K280" t="n">
         <v>2.888351156510363</v>
       </c>
     </row>
@@ -11117,6 +11959,9 @@
         </is>
       </c>
       <c r="J281" t="n">
+        <v>13</v>
+      </c>
+      <c r="K281" t="n">
         <v>2.881999475913747</v>
       </c>
     </row>
@@ -11155,6 +12000,9 @@
         </is>
       </c>
       <c r="J282" t="n">
+        <v>13</v>
+      </c>
+      <c r="K282" t="n">
         <v>2.881999475913747</v>
       </c>
     </row>
@@ -11193,6 +12041,9 @@
         </is>
       </c>
       <c r="J283" t="n">
+        <v>13</v>
+      </c>
+      <c r="K283" t="n">
         <v>2.881999475913747</v>
       </c>
     </row>
@@ -11231,6 +12082,9 @@
         </is>
       </c>
       <c r="J284" t="n">
+        <v>13</v>
+      </c>
+      <c r="K284" t="n">
         <v>2.931696851688956</v>
       </c>
     </row>
@@ -11269,6 +12123,9 @@
         </is>
       </c>
       <c r="J285" t="n">
+        <v>13</v>
+      </c>
+      <c r="K285" t="n">
         <v>3.052324611637583</v>
       </c>
     </row>
@@ -11307,6 +12164,9 @@
         </is>
       </c>
       <c r="J286" t="n">
+        <v>13</v>
+      </c>
+      <c r="K286" t="n">
         <v>3.117026603886375</v>
       </c>
     </row>
@@ -11345,6 +12205,9 @@
         </is>
       </c>
       <c r="J287" t="n">
+        <v>13</v>
+      </c>
+      <c r="K287" t="n">
         <v>3.117026603886375</v>
       </c>
     </row>
@@ -11383,6 +12246,9 @@
         </is>
       </c>
       <c r="J288" t="n">
+        <v>13</v>
+      </c>
+      <c r="K288" t="n">
         <v>3.220727790183071</v>
       </c>
     </row>
@@ -11421,6 +12287,9 @@
         </is>
       </c>
       <c r="J289" t="n">
+        <v>13</v>
+      </c>
+      <c r="K289" t="n">
         <v>3.220727790183071</v>
       </c>
     </row>
@@ -11459,6 +12328,9 @@
         </is>
       </c>
       <c r="J290" t="n">
+        <v>13</v>
+      </c>
+      <c r="K290" t="n">
         <v>3.206267301468427</v>
       </c>
     </row>
@@ -11497,6 +12369,9 @@
         </is>
       </c>
       <c r="J291" t="n">
+        <v>13</v>
+      </c>
+      <c r="K291" t="n">
         <v>3.220069684849563</v>
       </c>
     </row>
@@ -11535,6 +12410,9 @@
         </is>
       </c>
       <c r="J292" t="n">
+        <v>13</v>
+      </c>
+      <c r="K292" t="n">
         <v>3.220069684849563</v>
       </c>
     </row>
@@ -11573,6 +12451,9 @@
         </is>
       </c>
       <c r="J293" t="n">
+        <v>13</v>
+      </c>
+      <c r="K293" t="n">
         <v>3.139266230842714</v>
       </c>
     </row>
@@ -11611,6 +12492,9 @@
         </is>
       </c>
       <c r="J294" t="n">
+        <v>13</v>
+      </c>
+      <c r="K294" t="n">
         <v>3.051782695598409</v>
       </c>
     </row>
@@ -11649,6 +12533,9 @@
         </is>
       </c>
       <c r="J295" t="n">
+        <v>13</v>
+      </c>
+      <c r="K295" t="n">
         <v>3.01812345520382</v>
       </c>
     </row>
@@ -11687,6 +12574,9 @@
         </is>
       </c>
       <c r="J296" t="n">
+        <v>13</v>
+      </c>
+      <c r="K296" t="n">
         <v>2.950236123276051</v>
       </c>
     </row>
@@ -11725,6 +12615,9 @@
         </is>
       </c>
       <c r="J297" t="n">
+        <v>13</v>
+      </c>
+      <c r="K297" t="n">
         <v>2.933064446758998</v>
       </c>
     </row>
@@ -11763,6 +12656,9 @@
         </is>
       </c>
       <c r="J298" t="n">
+        <v>13</v>
+      </c>
+      <c r="K298" t="n">
         <v>2.969099575318594</v>
       </c>
     </row>
@@ -11801,6 +12697,9 @@
         </is>
       </c>
       <c r="J299" t="n">
+        <v>13</v>
+      </c>
+      <c r="K299" t="n">
         <v>3.064871311042366</v>
       </c>
     </row>
@@ -11839,6 +12738,9 @@
         </is>
       </c>
       <c r="J300" t="n">
+        <v>13</v>
+      </c>
+      <c r="K300" t="n">
         <v>3.114581492814289</v>
       </c>
     </row>
@@ -11877,6 +12779,9 @@
         </is>
       </c>
       <c r="J301" t="n">
+        <v>13</v>
+      </c>
+      <c r="K301" t="n">
         <v>3.114581492814289</v>
       </c>
     </row>
@@ -11915,6 +12820,9 @@
         </is>
       </c>
       <c r="J302" t="n">
+        <v>13</v>
+      </c>
+      <c r="K302" t="n">
         <v>3.209482865352926</v>
       </c>
     </row>
@@ -11953,6 +12861,9 @@
         </is>
       </c>
       <c r="J303" t="n">
+        <v>13</v>
+      </c>
+      <c r="K303" t="n">
         <v>3.206758643135085</v>
       </c>
     </row>
@@ -11991,6 +12902,9 @@
         </is>
       </c>
       <c r="J304" t="n">
+        <v>13</v>
+      </c>
+      <c r="K304" t="n">
         <v>3.056589363345596</v>
       </c>
     </row>
@@ -12029,6 +12943,9 @@
         </is>
       </c>
       <c r="J305" t="n">
+        <v>13</v>
+      </c>
+      <c r="K305" t="n">
         <v>2.919437395450269</v>
       </c>
     </row>
@@ -12067,6 +12984,9 @@
         </is>
       </c>
       <c r="J306" t="n">
+        <v>13</v>
+      </c>
+      <c r="K306" t="n">
         <v>2.611732014808289</v>
       </c>
     </row>
@@ -12105,6 +13025,9 @@
         </is>
       </c>
       <c r="J307" t="n">
+        <v>13</v>
+      </c>
+      <c r="K307" t="n">
         <v>2.490075315065341</v>
       </c>
     </row>
@@ -12143,6 +13066,9 @@
         </is>
       </c>
       <c r="J308" t="n">
+        <v>13</v>
+      </c>
+      <c r="K308" t="n">
         <v>2.490075315065341</v>
       </c>
     </row>
@@ -12181,6 +13107,9 @@
         </is>
       </c>
       <c r="J309" t="n">
+        <v>13</v>
+      </c>
+      <c r="K309" t="n">
         <v>2.333084993733451</v>
       </c>
     </row>
@@ -12219,6 +13148,9 @@
         </is>
       </c>
       <c r="J310" t="n">
+        <v>13</v>
+      </c>
+      <c r="K310" t="n">
         <v>2.470062220214085</v>
       </c>
     </row>
@@ -12257,6 +13189,9 @@
         </is>
       </c>
       <c r="J311" t="n">
+        <v>13</v>
+      </c>
+      <c r="K311" t="n">
         <v>2.760853338379711</v>
       </c>
     </row>
@@ -12295,6 +13230,9 @@
         </is>
       </c>
       <c r="J312" t="n">
+        <v>13</v>
+      </c>
+      <c r="K312" t="n">
         <v>2.831024448893697</v>
       </c>
     </row>
@@ -12333,6 +13271,9 @@
         </is>
       </c>
       <c r="J313" t="n">
+        <v>13</v>
+      </c>
+      <c r="K313" t="n">
         <v>2.896485726977652</v>
       </c>
     </row>
@@ -12371,6 +13312,9 @@
         </is>
       </c>
       <c r="J314" t="n">
+        <v>13</v>
+      </c>
+      <c r="K314" t="n">
         <v>3.138094025778499</v>
       </c>
     </row>
@@ -12409,6 +13353,9 @@
         </is>
       </c>
       <c r="J315" t="n">
+        <v>13</v>
+      </c>
+      <c r="K315" t="n">
         <v>3.158030590125978</v>
       </c>
     </row>
@@ -12447,6 +13394,9 @@
         </is>
       </c>
       <c r="J316" t="n">
+        <v>13</v>
+      </c>
+      <c r="K316" t="n">
         <v>2.957986706022475</v>
       </c>
     </row>
@@ -12485,6 +13435,9 @@
         </is>
       </c>
       <c r="J317" t="n">
+        <v>13</v>
+      </c>
+      <c r="K317" t="n">
         <v>2.783391016408475</v>
       </c>
     </row>
@@ -12523,6 +13476,9 @@
         </is>
       </c>
       <c r="J318" t="n">
+        <v>13</v>
+      </c>
+      <c r="K318" t="n">
         <v>2.781725254660016</v>
       </c>
     </row>
@@ -12561,6 +13517,9 @@
         </is>
       </c>
       <c r="J319" t="n">
+        <v>13</v>
+      </c>
+      <c r="K319" t="n">
         <v>2.807824474919309</v>
       </c>
     </row>
@@ -12599,6 +13558,9 @@
         </is>
       </c>
       <c r="J320" t="n">
+        <v>13</v>
+      </c>
+      <c r="K320" t="n">
         <v>2.807824474919309</v>
       </c>
     </row>
@@ -12637,6 +13599,9 @@
         </is>
       </c>
       <c r="J321" t="n">
+        <v>13</v>
+      </c>
+      <c r="K321" t="n">
         <v>2.946118361960409</v>
       </c>
     </row>
@@ -12675,6 +13640,9 @@
         </is>
       </c>
       <c r="J322" t="n">
+        <v>13</v>
+      </c>
+      <c r="K322" t="n">
         <v>2.959890013121888</v>
       </c>
     </row>
@@ -12713,6 +13681,9 @@
         </is>
       </c>
       <c r="J323" t="n">
+        <v>13</v>
+      </c>
+      <c r="K323" t="n">
         <v>2.959890013121888</v>
       </c>
     </row>
@@ -12751,6 +13722,9 @@
         </is>
       </c>
       <c r="J324" t="n">
+        <v>13</v>
+      </c>
+      <c r="K324" t="n">
         <v>2.920106593276818</v>
       </c>
     </row>
@@ -12789,6 +13763,9 @@
         </is>
       </c>
       <c r="J325" t="n">
+        <v>13</v>
+      </c>
+      <c r="K325" t="n">
         <v>2.824455462485941</v>
       </c>
     </row>
@@ -12827,6 +13804,9 @@
         </is>
       </c>
       <c r="J326" t="n">
+        <v>13</v>
+      </c>
+      <c r="K326" t="n">
         <v>2.694576033673506</v>
       </c>
     </row>
@@ -12865,6 +13845,9 @@
         </is>
       </c>
       <c r="J327" t="n">
+        <v>13</v>
+      </c>
+      <c r="K327" t="n">
         <v>2.542914879365028</v>
       </c>
     </row>
@@ -12903,6 +13886,9 @@
         </is>
       </c>
       <c r="J328" t="n">
+        <v>13</v>
+      </c>
+      <c r="K328" t="n">
         <v>2.542914879365028</v>
       </c>
     </row>
@@ -12941,6 +13927,9 @@
         </is>
       </c>
       <c r="J329" t="n">
+        <v>13</v>
+      </c>
+      <c r="K329" t="n">
         <v>2.388320281588208</v>
       </c>
     </row>
@@ -12979,6 +13968,9 @@
         </is>
       </c>
       <c r="J330" t="n">
+        <v>13</v>
+      </c>
+      <c r="K330" t="n">
         <v>2.059868044147878</v>
       </c>
     </row>
@@ -13017,6 +14009,9 @@
         </is>
       </c>
       <c r="J331" t="n">
+        <v>13</v>
+      </c>
+      <c r="K331" t="n">
         <v>1.90235679214078</v>
       </c>
     </row>
@@ -13055,6 +14050,9 @@
         </is>
       </c>
       <c r="J332" t="n">
+        <v>13</v>
+      </c>
+      <c r="K332" t="n">
         <v>1.90235679214078</v>
       </c>
     </row>
@@ -13093,6 +14091,9 @@
         </is>
       </c>
       <c r="J333" t="n">
+        <v>13</v>
+      </c>
+      <c r="K333" t="n">
         <v>1.721349577604772</v>
       </c>
     </row>
@@ -13131,6 +14132,9 @@
         </is>
       </c>
       <c r="J334" t="n">
+        <v>13</v>
+      </c>
+      <c r="K334" t="n">
         <v>1.698503598909412</v>
       </c>
     </row>
@@ -13169,6 +14173,9 @@
         </is>
       </c>
       <c r="J335" t="n">
+        <v>13</v>
+      </c>
+      <c r="K335" t="n">
         <v>1.651663073750607</v>
       </c>
     </row>
@@ -13207,6 +14214,9 @@
         </is>
       </c>
       <c r="J336" t="n">
+        <v>13</v>
+      </c>
+      <c r="K336" t="n">
         <v>1.640962655131619</v>
       </c>
     </row>
@@ -13245,6 +14255,9 @@
         </is>
       </c>
       <c r="J337" t="n">
+        <v>13</v>
+      </c>
+      <c r="K337" t="n">
         <v>1.561481941261449</v>
       </c>
     </row>
@@ -13283,6 +14296,9 @@
         </is>
       </c>
       <c r="J338" t="n">
+        <v>13</v>
+      </c>
+      <c r="K338" t="n">
         <v>1.553402052511876</v>
       </c>
     </row>
@@ -13321,6 +14337,9 @@
         </is>
       </c>
       <c r="J339" t="n">
+        <v>13</v>
+      </c>
+      <c r="K339" t="n">
         <v>1.553402052511876</v>
       </c>
     </row>
@@ -13359,6 +14378,9 @@
         </is>
       </c>
       <c r="J340" t="n">
+        <v>13</v>
+      </c>
+      <c r="K340" t="n">
         <v>1.558134622278291</v>
       </c>
     </row>
@@ -13397,6 +14419,9 @@
         </is>
       </c>
       <c r="J341" t="n">
+        <v>13</v>
+      </c>
+      <c r="K341" t="n">
         <v>1.592535875313988</v>
       </c>
     </row>
@@ -13435,6 +14460,9 @@
         </is>
       </c>
       <c r="J342" t="n">
+        <v>13</v>
+      </c>
+      <c r="K342" t="n">
         <v>1.581930598851415</v>
       </c>
     </row>
@@ -13473,6 +14501,9 @@
         </is>
       </c>
       <c r="J343" t="n">
+        <v>13</v>
+      </c>
+      <c r="K343" t="n">
         <v>1.581930598851415</v>
       </c>
     </row>
@@ -13511,6 +14542,9 @@
         </is>
       </c>
       <c r="J344" t="n">
+        <v>13</v>
+      </c>
+      <c r="K344" t="n">
         <v>1.568189773827232</v>
       </c>
     </row>
@@ -13549,6 +14583,9 @@
         </is>
       </c>
       <c r="J345" t="n">
+        <v>13</v>
+      </c>
+      <c r="K345" t="n">
         <v>1.568189773827232</v>
       </c>
     </row>
@@ -13587,6 +14624,9 @@
         </is>
       </c>
       <c r="J346" t="n">
+        <v>13</v>
+      </c>
+      <c r="K346" t="n">
         <v>1.536087651858876</v>
       </c>
     </row>
@@ -13625,6 +14665,9 @@
         </is>
       </c>
       <c r="J347" t="n">
+        <v>13</v>
+      </c>
+      <c r="K347" t="n">
         <v>1.567914364678312</v>
       </c>
     </row>
@@ -13663,6 +14706,9 @@
         </is>
       </c>
       <c r="J348" t="n">
+        <v>13</v>
+      </c>
+      <c r="K348" t="n">
         <v>1.952976055882561</v>
       </c>
     </row>
@@ -13701,6 +14747,9 @@
         </is>
       </c>
       <c r="J349" t="n">
+        <v>13</v>
+      </c>
+      <c r="K349" t="n">
         <v>1.952976055882561</v>
       </c>
     </row>
@@ -13739,6 +14788,9 @@
         </is>
       </c>
       <c r="J350" t="n">
+        <v>13</v>
+      </c>
+      <c r="K350" t="n">
         <v>1.952976055882561</v>
       </c>
     </row>
@@ -13777,6 +14829,9 @@
         </is>
       </c>
       <c r="J351" t="n">
+        <v>13</v>
+      </c>
+      <c r="K351" t="n">
         <v>2.494303518880437</v>
       </c>
     </row>
@@ -13815,6 +14870,9 @@
         </is>
       </c>
       <c r="J352" t="n">
+        <v>13</v>
+      </c>
+      <c r="K352" t="n">
         <v>2.765479861290443</v>
       </c>
     </row>
@@ -13853,6 +14911,9 @@
         </is>
       </c>
       <c r="J353" t="n">
+        <v>13</v>
+      </c>
+      <c r="K353" t="n">
         <v>2.765479861290443</v>
       </c>
     </row>
@@ -13891,6 +14952,9 @@
         </is>
       </c>
       <c r="J354" t="n">
+        <v>13</v>
+      </c>
+      <c r="K354" t="n">
         <v>2.765479861290443</v>
       </c>
     </row>
@@ -13929,6 +14993,9 @@
         </is>
       </c>
       <c r="J355" t="n">
+        <v>13</v>
+      </c>
+      <c r="K355" t="n">
         <v>3.046028552446972</v>
       </c>
     </row>
@@ -13967,6 +15034,9 @@
         </is>
       </c>
       <c r="J356" t="n">
+        <v>13</v>
+      </c>
+      <c r="K356" t="n">
         <v>3.100813226182276</v>
       </c>
     </row>
@@ -14005,6 +15075,9 @@
         </is>
       </c>
       <c r="J357" t="n">
+        <v>13</v>
+      </c>
+      <c r="K357" t="n">
         <v>2.828640373609562</v>
       </c>
     </row>
@@ -14043,6 +15116,9 @@
         </is>
       </c>
       <c r="J358" t="n">
+        <v>13</v>
+      </c>
+      <c r="K358" t="n">
         <v>2.828640373609562</v>
       </c>
     </row>
@@ -14081,6 +15157,9 @@
         </is>
       </c>
       <c r="J359" t="n">
+        <v>13</v>
+      </c>
+      <c r="K359" t="n">
         <v>2.731107144267778</v>
       </c>
     </row>
@@ -14119,6 +15198,9 @@
         </is>
       </c>
       <c r="J360" t="n">
+        <v>13</v>
+      </c>
+      <c r="K360" t="n">
         <v>2.483879001518723</v>
       </c>
     </row>
@@ -14157,6 +15239,9 @@
         </is>
       </c>
       <c r="J361" t="n">
+        <v>13</v>
+      </c>
+      <c r="K361" t="n">
         <v>2.483879001518723</v>
       </c>
     </row>
@@ -14195,6 +15280,9 @@
         </is>
       </c>
       <c r="J362" t="n">
+        <v>13</v>
+      </c>
+      <c r="K362" t="n">
         <v>2.483879001518723</v>
       </c>
     </row>
@@ -14233,6 +15321,9 @@
         </is>
       </c>
       <c r="J363" t="n">
+        <v>13</v>
+      </c>
+      <c r="K363" t="n">
         <v>2.380256929299152</v>
       </c>
     </row>
@@ -14271,6 +15362,9 @@
         </is>
       </c>
       <c r="J364" t="n">
+        <v>13</v>
+      </c>
+      <c r="K364" t="n">
         <v>2.361346344683295</v>
       </c>
     </row>
@@ -14309,6 +15403,9 @@
         </is>
       </c>
       <c r="J365" t="n">
+        <v>13</v>
+      </c>
+      <c r="K365" t="n">
         <v>2.372434835599062</v>
       </c>
     </row>
@@ -14347,6 +15444,9 @@
         </is>
       </c>
       <c r="J366" t="n">
+        <v>13</v>
+      </c>
+      <c r="K366" t="n">
         <v>2.345564094498081</v>
       </c>
     </row>
@@ -14385,6 +15485,9 @@
         </is>
       </c>
       <c r="J367" t="n">
+        <v>13</v>
+      </c>
+      <c r="K367" t="n">
         <v>2.213527183372355</v>
       </c>
     </row>
@@ -14423,6 +15526,9 @@
         </is>
       </c>
       <c r="J368" t="n">
+        <v>13</v>
+      </c>
+      <c r="K368" t="n">
         <v>1.975941673361365</v>
       </c>
     </row>
@@ -14461,6 +15567,9 @@
         </is>
       </c>
       <c r="J369" t="n">
+        <v>13</v>
+      </c>
+      <c r="K369" t="n">
         <v>1.975941673361365</v>
       </c>
     </row>
@@ -14499,6 +15608,9 @@
         </is>
       </c>
       <c r="J370" t="n">
+        <v>13</v>
+      </c>
+      <c r="K370" t="n">
         <v>1.865613372365461</v>
       </c>
     </row>
@@ -14537,6 +15649,9 @@
         </is>
       </c>
       <c r="J371" t="n">
+        <v>13</v>
+      </c>
+      <c r="K371" t="n">
         <v>1.666097909423621</v>
       </c>
     </row>
@@ -14575,6 +15690,9 @@
         </is>
       </c>
       <c r="J372" t="n">
+        <v>13</v>
+      </c>
+      <c r="K372" t="n">
         <v>1.506313009646927</v>
       </c>
     </row>
@@ -14613,6 +15731,9 @@
         </is>
       </c>
       <c r="J373" t="n">
+        <v>13</v>
+      </c>
+      <c r="K373" t="n">
         <v>1.506313009646927</v>
       </c>
     </row>
@@ -14651,6 +15772,9 @@
         </is>
       </c>
       <c r="J374" t="n">
+        <v>13</v>
+      </c>
+      <c r="K374" t="n">
         <v>1.449329550034161</v>
       </c>
     </row>
@@ -14689,6 +15813,9 @@
         </is>
       </c>
       <c r="J375" t="n">
+        <v>13</v>
+      </c>
+      <c r="K375" t="n">
         <v>1.397985058834273</v>
       </c>
     </row>
@@ -14727,6 +15854,9 @@
         </is>
       </c>
       <c r="J376" t="n">
+        <v>13</v>
+      </c>
+      <c r="K376" t="n">
         <v>1.351557030145482</v>
       </c>
     </row>
@@ -14765,6 +15895,9 @@
         </is>
       </c>
       <c r="J377" t="n">
+        <v>13</v>
+      </c>
+      <c r="K377" t="n">
         <v>1.305351778442707</v>
       </c>
     </row>
@@ -14803,6 +15936,9 @@
         </is>
       </c>
       <c r="J378" t="n">
+        <v>13</v>
+      </c>
+      <c r="K378" t="n">
         <v>1.298901247902165</v>
       </c>
     </row>
@@ -14841,6 +15977,9 @@
         </is>
       </c>
       <c r="J379" t="n">
+        <v>13</v>
+      </c>
+      <c r="K379" t="n">
         <v>1.325150959140536</v>
       </c>
     </row>
@@ -14879,6 +16018,9 @@
         </is>
       </c>
       <c r="J380" t="n">
+        <v>13</v>
+      </c>
+      <c r="K380" t="n">
         <v>1.415467175486323</v>
       </c>
     </row>
@@ -14917,6 +16059,9 @@
         </is>
       </c>
       <c r="J381" t="n">
+        <v>13</v>
+      </c>
+      <c r="K381" t="n">
         <v>1.468564760461942</v>
       </c>
     </row>
@@ -14955,6 +16100,9 @@
         </is>
       </c>
       <c r="J382" t="n">
+        <v>13</v>
+      </c>
+      <c r="K382" t="n">
         <v>1.53165346771304</v>
       </c>
     </row>
@@ -14993,6 +16141,9 @@
         </is>
       </c>
       <c r="J383" t="n">
+        <v>13</v>
+      </c>
+      <c r="K383" t="n">
         <v>1.605584350685485</v>
       </c>
     </row>
@@ -15031,6 +16182,9 @@
         </is>
       </c>
       <c r="J384" t="n">
+        <v>13</v>
+      </c>
+      <c r="K384" t="n">
         <v>1.839479514257422</v>
       </c>
     </row>
@@ -15069,6 +16223,9 @@
         </is>
       </c>
       <c r="J385" t="n">
+        <v>13</v>
+      </c>
+      <c r="K385" t="n">
         <v>1.907695024717555</v>
       </c>
     </row>
@@ -15107,6 +16264,9 @@
         </is>
       </c>
       <c r="J386" t="n">
+        <v>13</v>
+      </c>
+      <c r="K386" t="n">
         <v>1.907695024717555</v>
       </c>
     </row>
@@ -15145,6 +16305,9 @@
         </is>
       </c>
       <c r="J387" t="n">
+        <v>13</v>
+      </c>
+      <c r="K387" t="n">
         <v>2.098392900454576</v>
       </c>
     </row>
@@ -15183,6 +16346,9 @@
         </is>
       </c>
       <c r="J388" t="n">
+        <v>13</v>
+      </c>
+      <c r="K388" t="n">
         <v>2.125893996626484</v>
       </c>
     </row>
@@ -15221,6 +16387,9 @@
         </is>
       </c>
       <c r="J389" t="n">
+        <v>13</v>
+      </c>
+      <c r="K389" t="n">
         <v>2.156690347619346</v>
       </c>
     </row>
@@ -15259,6 +16428,9 @@
         </is>
       </c>
       <c r="J390" t="n">
+        <v>13</v>
+      </c>
+      <c r="K390" t="n">
         <v>2.144931093967293</v>
       </c>
     </row>
@@ -15297,6 +16469,9 @@
         </is>
       </c>
       <c r="J391" t="n">
+        <v>13</v>
+      </c>
+      <c r="K391" t="n">
         <v>2.144931093967293</v>
       </c>
     </row>
@@ -15335,6 +16510,9 @@
         </is>
       </c>
       <c r="J392" t="n">
+        <v>13</v>
+      </c>
+      <c r="K392" t="n">
         <v>1.977705179743598</v>
       </c>
     </row>
@@ -15373,6 +16551,9 @@
         </is>
       </c>
       <c r="J393" t="n">
+        <v>13</v>
+      </c>
+      <c r="K393" t="n">
         <v>1.977705179743598</v>
       </c>
     </row>
@@ -15411,6 +16592,9 @@
         </is>
       </c>
       <c r="J394" t="n">
+        <v>13</v>
+      </c>
+      <c r="K394" t="n">
         <v>1.876517727390925</v>
       </c>
     </row>
@@ -15449,6 +16633,9 @@
         </is>
       </c>
       <c r="J395" t="n">
+        <v>13</v>
+      </c>
+      <c r="K395" t="n">
         <v>1.793464093134713</v>
       </c>
     </row>
@@ -15487,6 +16674,9 @@
         </is>
       </c>
       <c r="J396" t="n">
+        <v>13</v>
+      </c>
+      <c r="K396" t="n">
         <v>1.793464093134713</v>
       </c>
     </row>
@@ -15525,6 +16715,9 @@
         </is>
       </c>
       <c r="J397" t="n">
+        <v>13</v>
+      </c>
+      <c r="K397" t="n">
         <v>1.777659199519649</v>
       </c>
     </row>
@@ -15563,6 +16756,9 @@
         </is>
       </c>
       <c r="J398" t="n">
+        <v>13</v>
+      </c>
+      <c r="K398" t="n">
         <v>1.8015959309684</v>
       </c>
     </row>
@@ -15601,6 +16797,9 @@
         </is>
       </c>
       <c r="J399" t="n">
+        <v>13</v>
+      </c>
+      <c r="K399" t="n">
         <v>1.8015959309684</v>
       </c>
     </row>
@@ -15639,6 +16838,9 @@
         </is>
       </c>
       <c r="J400" t="n">
+        <v>13</v>
+      </c>
+      <c r="K400" t="n">
         <v>1.781521394405934</v>
       </c>
     </row>
@@ -15677,6 +16879,9 @@
         </is>
       </c>
       <c r="J401" t="n">
+        <v>13</v>
+      </c>
+      <c r="K401" t="n">
         <v>1.707767716195527</v>
       </c>
     </row>
@@ -15715,6 +16920,9 @@
         </is>
       </c>
       <c r="J402" t="n">
+        <v>13</v>
+      </c>
+      <c r="K402" t="n">
         <v>1.676679034812198</v>
       </c>
     </row>
@@ -15753,6 +16961,9 @@
         </is>
       </c>
       <c r="J403" t="n">
+        <v>13</v>
+      </c>
+      <c r="K403" t="n">
         <v>1.676679034812198</v>
       </c>
     </row>
@@ -15791,6 +17002,9 @@
         </is>
       </c>
       <c r="J404" t="n">
+        <v>13</v>
+      </c>
+      <c r="K404" t="n">
         <v>1.588453590568637</v>
       </c>
     </row>
@@ -15829,6 +17043,9 @@
         </is>
       </c>
       <c r="J405" t="n">
+        <v>13</v>
+      </c>
+      <c r="K405" t="n">
         <v>1.541416976561704</v>
       </c>
     </row>
@@ -15867,6 +17084,9 @@
         </is>
       </c>
       <c r="J406" t="n">
+        <v>13</v>
+      </c>
+      <c r="K406" t="n">
         <v>1.461973390111028</v>
       </c>
     </row>
@@ -15905,6 +17125,9 @@
         </is>
       </c>
       <c r="J407" t="n">
+        <v>13</v>
+      </c>
+      <c r="K407" t="n">
         <v>1.461973390111028</v>
       </c>
     </row>
@@ -15943,6 +17166,9 @@
         </is>
       </c>
       <c r="J408" t="n">
+        <v>13</v>
+      </c>
+      <c r="K408" t="n">
         <v>1.299924719804793</v>
       </c>
     </row>
@@ -15981,6 +17207,9 @@
         </is>
       </c>
       <c r="J409" t="n">
+        <v>13</v>
+      </c>
+      <c r="K409" t="n">
         <v>1.299924719804793</v>
       </c>
     </row>
@@ -16019,6 +17248,9 @@
         </is>
       </c>
       <c r="J410" t="n">
+        <v>13</v>
+      </c>
+      <c r="K410" t="n">
         <v>1.299924719804793</v>
       </c>
     </row>
@@ -16057,6 +17289,9 @@
         </is>
       </c>
       <c r="J411" t="n">
+        <v>13</v>
+      </c>
+      <c r="K411" t="n">
         <v>1.234009848682012</v>
       </c>
     </row>
@@ -16095,6 +17330,9 @@
         </is>
       </c>
       <c r="J412" t="n">
+        <v>13</v>
+      </c>
+      <c r="K412" t="n">
         <v>1.234009848682012</v>
       </c>
     </row>
@@ -16133,6 +17371,9 @@
         </is>
       </c>
       <c r="J413" t="n">
+        <v>13</v>
+      </c>
+      <c r="K413" t="n">
         <v>1.163607608399603</v>
       </c>
     </row>
@@ -16171,6 +17412,9 @@
         </is>
       </c>
       <c r="J414" t="n">
+        <v>13</v>
+      </c>
+      <c r="K414" t="n">
         <v>1.108748276134141</v>
       </c>
     </row>
@@ -16209,6 +17453,9 @@
         </is>
       </c>
       <c r="J415" t="n">
+        <v>13</v>
+      </c>
+      <c r="K415" t="n">
         <v>1.108748276134141</v>
       </c>
     </row>
@@ -16247,6 +17494,9 @@
         </is>
       </c>
       <c r="J416" t="n">
+        <v>13</v>
+      </c>
+      <c r="K416" t="n">
         <v>1.108748276134141</v>
       </c>
     </row>
@@ -16285,6 +17535,9 @@
         </is>
       </c>
       <c r="J417" t="n">
+        <v>13</v>
+      </c>
+      <c r="K417" t="n">
         <v>1.143908926624225</v>
       </c>
     </row>
@@ -16323,6 +17576,9 @@
         </is>
       </c>
       <c r="J418" t="n">
+        <v>13</v>
+      </c>
+      <c r="K418" t="n">
         <v>1.143908926624225</v>
       </c>
     </row>
@@ -16361,6 +17617,9 @@
         </is>
       </c>
       <c r="J419" t="n">
+        <v>13</v>
+      </c>
+      <c r="K419" t="n">
         <v>1.17283296788326</v>
       </c>
     </row>
@@ -16399,6 +17658,9 @@
         </is>
       </c>
       <c r="J420" t="n">
+        <v>13</v>
+      </c>
+      <c r="K420" t="n">
         <v>1.197101282903176</v>
       </c>
     </row>
@@ -16437,6 +17699,9 @@
         </is>
       </c>
       <c r="J421" t="n">
+        <v>13</v>
+      </c>
+      <c r="K421" t="n">
         <v>1.340723206750572</v>
       </c>
     </row>
@@ -16475,6 +17740,9 @@
         </is>
       </c>
       <c r="J422" t="n">
+        <v>13</v>
+      </c>
+      <c r="K422" t="n">
         <v>1.387922623419854</v>
       </c>
     </row>
@@ -16513,6 +17781,9 @@
         </is>
       </c>
       <c r="J423" t="n">
+        <v>13</v>
+      </c>
+      <c r="K423" t="n">
         <v>1.528974275552455</v>
       </c>
     </row>
@@ -16551,6 +17822,9 @@
         </is>
       </c>
       <c r="J424" t="n">
+        <v>13</v>
+      </c>
+      <c r="K424" t="n">
         <v>1.528974275552455</v>
       </c>
     </row>
@@ -16589,6 +17863,9 @@
         </is>
       </c>
       <c r="J425" t="n">
+        <v>13</v>
+      </c>
+      <c r="K425" t="n">
         <v>1.528974275552455</v>
       </c>
     </row>
@@ -16627,6 +17904,9 @@
         </is>
       </c>
       <c r="J426" t="n">
+        <v>13</v>
+      </c>
+      <c r="K426" t="n">
         <v>1.519678996391473</v>
       </c>
     </row>

--- a/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B02_Normal_1.xlsx
+++ b/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B02_Normal_1.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>24.44938674448072</v>
+        <v>22.73756640125236</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>16.22537890841612</v>
+        <v>16.29324050952215</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>15.92519383307983</v>
+        <v>15.99543613326018</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>15.55123726155539</v>
+        <v>15.62439489880449</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>15.50392193361757</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86969785602394</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86959415022024</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>13.96252814601202</v>
+        <v>13.91864954866779</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>12.8845474029381</v>
+        <v>12.87463469178007</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>12.56557511094277</v>
+        <v>12.56213898660848</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>12.56557511094277</v>
+        <v>12.55954078162074</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>12.42650727241244</v>
+        <v>12.41804037237105</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>12.61222121789064</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>12.88726856229838</v>
+        <v>12.89114719647669</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>13.08268414389388</v>
+        <v>13.08601325120547</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>13.11655963642752</v>
+        <v>13.1112961343127</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>13.06477406907523</v>
+        <v>13.06050754757873</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>12.82946633796654</v>
+        <v>12.82287865109407</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>12.72199060197538</v>
+        <v>12.71927945377958</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>12.76786570293602</v>
+        <v>12.77031387086443</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>12.94918332241907</v>
+        <v>12.95485717835137</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29520804089071</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29710102990174</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>13.74461230569916</v>
+        <v>13.75403391875815</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>14.01711486461985</v>
+        <v>14.02366076953313</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>14.02341868198291</v>
+        <v>14.02914779581027</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>14.37286417316269</v>
+        <v>14.37156478609048</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>14.36056284287022</v>
+        <v>14.36020323793898</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>14.32918239439808</v>
+        <v>14.3290624341717</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>14.33140447444988</v>
+        <v>14.3325069672442</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>14.33266758623184</v>
+        <v>14.33386682670858</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>14.47432312940295</v>
+        <v>14.4778957262455</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>14.69408070284003</v>
+        <v>14.70491730440479</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>14.90097207929845</v>
+        <v>14.70491730440479</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>14.90097207929845</v>
+        <v>14.9139321578258</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>15.39058793177672</v>
+        <v>15.39818561758153</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>15.55279586015389</v>
+        <v>15.55789316181155</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>16.46410452789935</v>
+        <v>16.44727977295515</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.37544874440357</v>
+        <v>17.34712478394894</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>18.99504856873714</v>
+        <v>19.09058139794423</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>19.35440687995326</v>
+        <v>19.36955181416631</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>11</v>
       </c>
       <c r="K55" t="n">
-        <v>20.85858809627996</v>
+        <v>20.81524252050833</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>20.89169658899361</v>
+        <v>20.84331547113941</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>21.75595998124422</v>
+        <v>21.75006574949062</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>22.23426731578168</v>
+        <v>22.25305706353997</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>21.95138014089535</v>
+        <v>21.9712890272184</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>24.63649424087505</v>
+        <v>24.65959851968772</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>25.18536911583633</v>
+        <v>24.65959851968772</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>11</v>
       </c>
       <c r="K62" t="n">
-        <v>27.31329478260586</v>
+        <v>27.34628858172988</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>11</v>
       </c>
       <c r="K63" t="n">
-        <v>27.18205504873007</v>
+        <v>27.25367540568017</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>26.71182468007363</v>
+        <v>26.69655756684118</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>26.61477337250786</v>
+        <v>26.59925138949226</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>9.819882390104297</v>
+        <v>9.796381120057267</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>11</v>
       </c>
       <c r="K67" t="n">
-        <v>9.819882390104297</v>
+        <v>9.796381120057267</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>9.745667235392832</v>
+        <v>9.741185129511519</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>11</v>
       </c>
       <c r="K69" t="n">
-        <v>9.745667235392832</v>
+        <v>9.741185129511519</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>11</v>
       </c>
       <c r="K70" t="n">
-        <v>9.75609596068019</v>
+        <v>9.74618151868393</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>11</v>
       </c>
       <c r="K71" t="n">
-        <v>9.75609596068019</v>
+        <v>9.74618151868393</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>11</v>
       </c>
       <c r="K72" t="n">
-        <v>9.981290382682612</v>
+        <v>9.934397059286889</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>11</v>
       </c>
       <c r="K73" t="n">
-        <v>9.981290382682612</v>
+        <v>9.934397059286889</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>11</v>
       </c>
       <c r="K74" t="n">
-        <v>12.09167051507188</v>
+        <v>12.10118790918484</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>11</v>
       </c>
       <c r="K75" t="n">
-        <v>12.31620569749018</v>
+        <v>12.32151040736936</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="K76" t="n">
-        <v>12.66141284150133</v>
+        <v>12.66772849390226</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>11</v>
       </c>
       <c r="K77" t="n">
-        <v>13.00449390422686</v>
+        <v>12.9966977715787</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>11</v>
       </c>
       <c r="K78" t="n">
-        <v>9.12738816852228</v>
+        <v>9.12138807972668</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>11</v>
       </c>
       <c r="K79" t="n">
-        <v>8.68658704571123</v>
+        <v>8.685163559773121</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>11</v>
       </c>
       <c r="K80" t="n">
-        <v>8.681894726582</v>
+        <v>8.680606216873509</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>11</v>
       </c>
       <c r="K81" t="n">
-        <v>8.693004759293984</v>
+        <v>8.693592028238019</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>11</v>
       </c>
       <c r="K82" t="n">
-        <v>8.725149125649589</v>
+        <v>8.725792306726596</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>11</v>
       </c>
       <c r="K83" t="n">
-        <v>8.767374629969833</v>
+        <v>8.767927440838232</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="K84" t="n">
-        <v>8.810038227616156</v>
+        <v>8.811057918534789</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>11</v>
       </c>
       <c r="K85" t="n">
-        <v>8.810038227616156</v>
+        <v>8.811057918534789</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>11</v>
       </c>
       <c r="K86" t="n">
-        <v>8.979920966893374</v>
+        <v>8.981518238291311</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>11</v>
       </c>
       <c r="K87" t="n">
-        <v>9.189485465294592</v>
+        <v>9.191916534395689</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>11</v>
       </c>
       <c r="K88" t="n">
-        <v>9.20061339885968</v>
+        <v>9.202788083270709</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>11</v>
       </c>
       <c r="K89" t="n">
-        <v>9.385776211530537</v>
+        <v>9.388153658429088</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>11</v>
       </c>
       <c r="K90" t="n">
-        <v>9.385776211530537</v>
+        <v>9.388153658429088</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>11</v>
       </c>
       <c r="K91" t="n">
-        <v>9.594901878548837</v>
+        <v>9.597404951859314</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>11</v>
       </c>
       <c r="K92" t="n">
-        <v>9.711631620980414</v>
+        <v>9.714352824288483</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>11</v>
       </c>
       <c r="K93" t="n">
-        <v>9.812453513515775</v>
+        <v>9.815291677891272</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>11</v>
       </c>
       <c r="K94" t="n">
-        <v>9.974311185902952</v>
+        <v>9.97553945435223</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>11</v>
       </c>
       <c r="K95" t="n">
-        <v>10.02205133288883</v>
+        <v>10.02345565142805</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>11</v>
       </c>
       <c r="K96" t="n">
-        <v>10.28025187896138</v>
+        <v>10.28152909818356</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>11</v>
       </c>
       <c r="K97" t="n">
-        <v>10.38618001855317</v>
+        <v>10.3872519732941</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>11</v>
       </c>
       <c r="K98" t="n">
-        <v>10.44776992585482</v>
+        <v>10.44898465681968</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>11</v>
       </c>
       <c r="K99" t="n">
-        <v>10.55026105538567</v>
+        <v>10.55078913230849</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>11</v>
       </c>
       <c r="K100" t="n">
-        <v>10.55640596549939</v>
+        <v>10.55568052545157</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>11</v>
       </c>
       <c r="K101" t="n">
-        <v>10.52219052114853</v>
+        <v>10.52133522511898</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>11</v>
       </c>
       <c r="K102" t="n">
-        <v>10.4808184702455</v>
+        <v>10.48015718504093</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>11</v>
       </c>
       <c r="K103" t="n">
-        <v>10.45075109019776</v>
+        <v>10.4501027583802</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>11</v>
       </c>
       <c r="K104" t="n">
-        <v>10.42180488538178</v>
+        <v>10.42127072509713</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>11</v>
       </c>
       <c r="K105" t="n">
-        <v>10.41806567842505</v>
+        <v>10.4176749266558</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>11</v>
       </c>
       <c r="K106" t="n">
-        <v>10.3885771773526</v>
+        <v>10.38882430504399</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>11</v>
       </c>
       <c r="K107" t="n">
-        <v>10.45060969889723</v>
+        <v>10.45129953850017</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>11</v>
       </c>
       <c r="K108" t="n">
-        <v>10.50364497429563</v>
+        <v>10.50448765753914</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>11</v>
       </c>
       <c r="K109" t="n">
-        <v>10.81779559383239</v>
+        <v>10.8198000389266</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="K110" t="n">
-        <v>10.9357231825844</v>
+        <v>10.93789873648171</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>11</v>
       </c>
       <c r="K111" t="n">
-        <v>11.55281843846564</v>
+        <v>11.55704364183319</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>11</v>
       </c>
       <c r="K112" t="n">
-        <v>13.24905110056308</v>
+        <v>13.31560369386983</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>11</v>
       </c>
       <c r="K113" t="n">
-        <v>13.24905110056308</v>
+        <v>13.31560369386983</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>11</v>
       </c>
       <c r="K114" t="n">
-        <v>13.96546733948439</v>
+        <v>14.40688162462841</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>11</v>
       </c>
       <c r="K115" t="n">
-        <v>14.09499060277884</v>
+        <v>14.09612157306057</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>11</v>
       </c>
       <c r="K116" t="n">
-        <v>14.10231971947695</v>
+        <v>14.10138450013956</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>11</v>
       </c>
       <c r="K117" t="n">
-        <v>13.32115312121745</v>
+        <v>13.326414149434</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>11</v>
       </c>
       <c r="K118" t="n">
-        <v>12.18673597949732</v>
+        <v>12.13198070255896</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>11</v>
       </c>
       <c r="K119" t="n">
-        <v>11.61520007469289</v>
+        <v>11.55600136387979</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>11</v>
       </c>
       <c r="K120" t="n">
-        <v>10.7717653162068</v>
+        <v>10.77116273756967</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>11</v>
       </c>
       <c r="K121" t="n">
-        <v>10.62118096941062</v>
+        <v>10.62822165545307</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>11</v>
       </c>
       <c r="K122" t="n">
-        <v>10.62118096941062</v>
+        <v>10.62822165545307</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>11</v>
       </c>
       <c r="K123" t="n">
-        <v>10.45511537631013</v>
+        <v>10.45563919377957</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>11</v>
       </c>
       <c r="K124" t="n">
-        <v>10.44611547119964</v>
+        <v>10.44624520062144</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>11</v>
       </c>
       <c r="K125" t="n">
-        <v>10.40516927885814</v>
+        <v>10.40283994622784</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>11</v>
       </c>
       <c r="K126" t="n">
-        <v>10.15234578612369</v>
+        <v>10.1516257817853</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>11</v>
       </c>
       <c r="K127" t="n">
-        <v>10.12854983494127</v>
+        <v>10.1268169564278</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>11</v>
       </c>
       <c r="K128" t="n">
-        <v>10.13429438631349</v>
+        <v>10.13136169448493</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>11</v>
       </c>
       <c r="K129" t="n">
-        <v>10.16702268282531</v>
+        <v>10.16258449880304</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>11</v>
       </c>
       <c r="K130" t="n">
-        <v>10.19850456500321</v>
+        <v>10.19799380980201</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="K131" t="n">
-        <v>10.15988699682155</v>
+        <v>10.1601319628132</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>11</v>
       </c>
       <c r="K132" t="n">
-        <v>10.15045600603868</v>
+        <v>10.15094173673778</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>11</v>
       </c>
       <c r="K133" t="n">
-        <v>10.15045600603868</v>
+        <v>10.15094173673778</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>11</v>
       </c>
       <c r="K134" t="n">
-        <v>9.889113576235221</v>
+        <v>9.889344493517445</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>11</v>
       </c>
       <c r="K135" t="n">
-        <v>9.889113576235221</v>
+        <v>9.889344493517445</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>11</v>
       </c>
       <c r="K136" t="n">
-        <v>9.503480022823256</v>
+        <v>9.502205430969047</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>11</v>
       </c>
       <c r="K137" t="n">
-        <v>9.503480022823256</v>
+        <v>9.502205430969047</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>11</v>
       </c>
       <c r="K138" t="n">
-        <v>9.273302827189962</v>
+        <v>9.2747641829085</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>11</v>
       </c>
       <c r="K139" t="n">
-        <v>9.323353732391949</v>
+        <v>9.324573665658882</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>11</v>
       </c>
       <c r="K140" t="n">
-        <v>9.538199059605576</v>
+        <v>9.538440518080224</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>11</v>
       </c>
       <c r="K141" t="n">
-        <v>9.595159351550077</v>
+        <v>9.595754876251377</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>11</v>
       </c>
       <c r="K142" t="n">
-        <v>9.640228187381412</v>
+        <v>9.635538819217883</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>11</v>
       </c>
       <c r="K143" t="n">
-        <v>9.67585678642285</v>
+        <v>9.660118069178658</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>11</v>
       </c>
       <c r="K144" t="n">
-        <v>9.67585678642285</v>
+        <v>9.660118069178658</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>11</v>
       </c>
       <c r="K145" t="n">
-        <v>9.644544295013892</v>
+        <v>9.630258149575942</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>11</v>
       </c>
       <c r="K146" t="n">
-        <v>9.575393468358264</v>
+        <v>9.568585070538559</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>11</v>
       </c>
       <c r="K147" t="n">
-        <v>9.509165247009472</v>
+        <v>9.501834150982846</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>11</v>
       </c>
       <c r="K148" t="n">
-        <v>9.186890150588898</v>
+        <v>9.182957295513431</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>11</v>
       </c>
       <c r="K149" t="n">
-        <v>8.892310645809815</v>
+        <v>8.890417392763156</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>11</v>
       </c>
       <c r="K150" t="n">
-        <v>8.798285875284799</v>
+        <v>8.798409828292209</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>11</v>
       </c>
       <c r="K151" t="n">
-        <v>8.875333945274798</v>
+        <v>8.875679267296459</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>11</v>
       </c>
       <c r="K152" t="n">
-        <v>8.916837319105506</v>
+        <v>8.916880621754231</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>11</v>
       </c>
       <c r="K153" t="n">
-        <v>9.076727962887233</v>
+        <v>9.078526140339113</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>11</v>
       </c>
       <c r="K154" t="n">
-        <v>9.266264516167034</v>
+        <v>9.26822225201467</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>11</v>
       </c>
       <c r="K155" t="n">
-        <v>9.383051777516972</v>
+        <v>9.385469462371724</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>11</v>
       </c>
       <c r="K156" t="n">
-        <v>9.383051777516972</v>
+        <v>9.385469462371724</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>11</v>
       </c>
       <c r="K157" t="n">
-        <v>9.460674517214896</v>
+        <v>9.460685228661809</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>11</v>
       </c>
       <c r="K158" t="n">
-        <v>9.460674517214896</v>
+        <v>9.460685228661809</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>11</v>
       </c>
       <c r="K159" t="n">
-        <v>9.459995832832561</v>
+        <v>9.459172912215124</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>11</v>
       </c>
       <c r="K160" t="n">
-        <v>9.459995832832561</v>
+        <v>9.459172912215124</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>11</v>
       </c>
       <c r="K161" t="n">
-        <v>9.442058385983874</v>
+        <v>9.44774546930241</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>11</v>
       </c>
       <c r="K162" t="n">
-        <v>9.44635359893042</v>
+        <v>9.450594952595399</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>11</v>
       </c>
       <c r="K163" t="n">
-        <v>9.44078455669402</v>
+        <v>9.450594952595399</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>11</v>
       </c>
       <c r="K164" t="n">
-        <v>9.44078455669402</v>
+        <v>9.450594952595399</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>11</v>
       </c>
       <c r="K165" t="n">
-        <v>9.436919149557639</v>
+        <v>9.423943260376005</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>11</v>
       </c>
       <c r="K166" t="n">
-        <v>9.471086390640769</v>
+        <v>9.460449798597436</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>11</v>
       </c>
       <c r="K167" t="n">
-        <v>9.471086390640769</v>
+        <v>9.460449798597436</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>11</v>
       </c>
       <c r="K168" t="n">
-        <v>9.471086390640769</v>
+        <v>9.460449798597436</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>11</v>
       </c>
       <c r="K169" t="n">
-        <v>9.558331869346324</v>
+        <v>9.554211314302702</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>13</v>
       </c>
       <c r="K170" t="n">
-        <v>10.55331911901448</v>
+        <v>10.55820295284939</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>13</v>
       </c>
       <c r="K171" t="n">
-        <v>10.97574274908715</v>
+        <v>10.98258523360701</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>13</v>
       </c>
       <c r="K172" t="n">
-        <v>12.49691388284474</v>
+        <v>12.50762580550621</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>13</v>
       </c>
       <c r="K173" t="n">
-        <v>13.23294049977152</v>
+        <v>13.24672667496017</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>13</v>
       </c>
       <c r="K174" t="n">
-        <v>14.14162708229524</v>
+        <v>14.15612351666697</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>13</v>
       </c>
       <c r="K175" t="n">
-        <v>15.08727790142</v>
+        <v>15.10067834774809</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>13</v>
       </c>
       <c r="K176" t="n">
-        <v>15.85430464949789</v>
+        <v>15.86357315391385</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>13</v>
       </c>
       <c r="K177" t="n">
-        <v>16.05225719177724</v>
+        <v>16.04804018118733</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>13</v>
       </c>
       <c r="K178" t="n">
-        <v>16.05225719177724</v>
+        <v>16.04804018118733</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>13</v>
       </c>
       <c r="K179" t="n">
-        <v>15.41681884273828</v>
+        <v>15.41270274668939</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>13</v>
       </c>
       <c r="K180" t="n">
-        <v>14.85223332821751</v>
+        <v>14.68317070044758</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>13</v>
       </c>
       <c r="K181" t="n">
-        <v>14.85223332821751</v>
+        <v>14.68317070044758</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>13</v>
       </c>
       <c r="K182" t="n">
-        <v>13.87028048897389</v>
+        <v>13.86914984016242</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>13</v>
       </c>
       <c r="K183" t="n">
-        <v>13.48909493485402</v>
+        <v>13.48766261256322</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>13</v>
       </c>
       <c r="K184" t="n">
-        <v>13.48909493485402</v>
+        <v>13.48766261256322</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>13</v>
       </c>
       <c r="K185" t="n">
-        <v>13.09392521274405</v>
+        <v>13.09331666773408</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>13</v>
       </c>
       <c r="K186" t="n">
-        <v>12.83928370268094</v>
+        <v>12.83868137708381</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>13</v>
       </c>
       <c r="K187" t="n">
-        <v>12.75220267877187</v>
+        <v>12.75139590734058</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>13</v>
       </c>
       <c r="K188" t="n">
-        <v>12.65161912803199</v>
+        <v>12.65093616381321</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>13</v>
       </c>
       <c r="K189" t="n">
-        <v>12.38198982180875</v>
+        <v>12.38078309746591</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>13</v>
       </c>
       <c r="K190" t="n">
-        <v>11.8071681535344</v>
+        <v>11.8061490401634</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>13</v>
       </c>
       <c r="K191" t="n">
-        <v>2.375343852709965</v>
+        <v>2.375445612636807</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>13</v>
       </c>
       <c r="K192" t="n">
-        <v>2.375343852709965</v>
+        <v>2.375445612636807</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>13</v>
       </c>
       <c r="K193" t="n">
-        <v>2.403093697979613</v>
+        <v>2.40334463178614</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>13</v>
       </c>
       <c r="K194" t="n">
-        <v>2.565977898371402</v>
+        <v>2.566294774730969</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>13</v>
       </c>
       <c r="K195" t="n">
-        <v>11.85212475762777</v>
+        <v>11.84943506802738</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>13</v>
       </c>
       <c r="K196" t="n">
-        <v>11.85212475762777</v>
+        <v>11.84943506802738</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>13</v>
       </c>
       <c r="K197" t="n">
-        <v>11.85212475762777</v>
+        <v>11.84943506802738</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>13</v>
       </c>
       <c r="K198" t="n">
-        <v>12.765658678647</v>
+        <v>11.95051818786886</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>13</v>
       </c>
       <c r="K199" t="n">
-        <v>13.38283727671386</v>
+        <v>11.87403804176488</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>13</v>
       </c>
       <c r="K200" t="n">
-        <v>13.38283727671386</v>
+        <v>11.87403804176488</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>13</v>
       </c>
       <c r="K201" t="n">
-        <v>13.38283727671386</v>
+        <v>11.87403804176488</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>13</v>
       </c>
       <c r="K202" t="n">
-        <v>13.38283727671386</v>
+        <v>11.87403804176488</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>13</v>
       </c>
       <c r="K203" t="n">
-        <v>13.38283727671386</v>
+        <v>11.87403804176488</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>13</v>
       </c>
       <c r="K204" t="n">
-        <v>11.841804383611</v>
+        <v>11.82521240622121</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>13</v>
       </c>
       <c r="K205" t="n">
-        <v>11.841804383611</v>
+        <v>11.82521240622121</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>13</v>
       </c>
       <c r="K206" t="n">
-        <v>11.841804383611</v>
+        <v>11.82521240622121</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>13</v>
       </c>
       <c r="K207" t="n">
-        <v>11.841804383611</v>
+        <v>11.82521240622121</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>13</v>
       </c>
       <c r="K208" t="n">
-        <v>11.5581609664542</v>
+        <v>11.55268475455953</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>13</v>
       </c>
       <c r="K209" t="n">
-        <v>2.182238964742554</v>
+        <v>2.182369730994207</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>13</v>
       </c>
       <c r="K210" t="n">
-        <v>1.908400853213792</v>
+        <v>1.908233412376355</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>13</v>
       </c>
       <c r="K211" t="n">
-        <v>1.928104875567422</v>
+        <v>1.928346583154023</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>13</v>
       </c>
       <c r="K212" t="n">
-        <v>1.928104875567422</v>
+        <v>1.928346583154023</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>13</v>
       </c>
       <c r="K213" t="n">
-        <v>1.946527496520316</v>
+        <v>1.946610923119271</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>13</v>
       </c>
       <c r="K214" t="n">
-        <v>2.000068265384438</v>
+        <v>2.000506256511577</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>13</v>
       </c>
       <c r="K215" t="n">
-        <v>2.000068265384438</v>
+        <v>2.000506256511577</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>13</v>
       </c>
       <c r="K216" t="n">
-        <v>2.228818630840926</v>
+        <v>2.226097467301622</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>13</v>
       </c>
       <c r="K217" t="n">
-        <v>2.228818630840926</v>
+        <v>2.226097467301622</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>13</v>
       </c>
       <c r="K218" t="n">
-        <v>2.501604773914607</v>
+        <v>2.501745369924081</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>13</v>
       </c>
       <c r="K219" t="n">
-        <v>2.501604773914607</v>
+        <v>2.501745369924081</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>13</v>
       </c>
       <c r="K220" t="n">
-        <v>2.501604773914607</v>
+        <v>2.501745369924081</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>13</v>
       </c>
       <c r="K221" t="n">
-        <v>2.864888144822098</v>
+        <v>2.870753377597752</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>13</v>
       </c>
       <c r="K222" t="n">
-        <v>3.094640752480634</v>
+        <v>3.09440929548348</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>13</v>
       </c>
       <c r="K223" t="n">
-        <v>3.272130625156524</v>
+        <v>3.272399189789111</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>13</v>
       </c>
       <c r="K224" t="n">
-        <v>3.293214151886771</v>
+        <v>3.293164923516126</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>13</v>
       </c>
       <c r="K225" t="n">
-        <v>3.293214151886771</v>
+        <v>3.293164923516126</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>13</v>
       </c>
       <c r="K226" t="n">
-        <v>3.239899719607355</v>
+        <v>3.278866697844077</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>13</v>
       </c>
       <c r="K227" t="n">
-        <v>3.19237736532465</v>
+        <v>3.191862900987527</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>13</v>
       </c>
       <c r="K228" t="n">
-        <v>3.133882975962623</v>
+        <v>3.132795175439036</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>13</v>
       </c>
       <c r="K229" t="n">
-        <v>3.133882975962623</v>
+        <v>3.132795175439036</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>13</v>
       </c>
       <c r="K230" t="n">
-        <v>3.044829795797425</v>
+        <v>3.043495719666795</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>13</v>
       </c>
       <c r="K231" t="n">
-        <v>2.899990053129708</v>
+        <v>2.896243721531414</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>13</v>
       </c>
       <c r="K232" t="n">
-        <v>2.899990053129708</v>
+        <v>2.896243721531414</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>13</v>
       </c>
       <c r="K233" t="n">
-        <v>2.733413616260812</v>
+        <v>2.728420750546538</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>13</v>
       </c>
       <c r="K234" t="n">
-        <v>2.733413616260812</v>
+        <v>2.728420750546538</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>13</v>
       </c>
       <c r="K235" t="n">
-        <v>2.423390682561244</v>
+        <v>2.420417136238828</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>13</v>
       </c>
       <c r="K236" t="n">
-        <v>2.423390682561244</v>
+        <v>2.420417136238828</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>13</v>
       </c>
       <c r="K237" t="n">
-        <v>2.423390682561244</v>
+        <v>2.420417136238828</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>13</v>
       </c>
       <c r="K238" t="n">
-        <v>2.271389242176518</v>
+        <v>2.267328656840621</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>13</v>
       </c>
       <c r="K239" t="n">
-        <v>2.02252475559434</v>
+        <v>2.019641742273688</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>13</v>
       </c>
       <c r="K240" t="n">
-        <v>1.960420584899899</v>
+        <v>1.959159793991466</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>13</v>
       </c>
       <c r="K241" t="n">
-        <v>1.922084617288877</v>
+        <v>1.92191103809226</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>13</v>
       </c>
       <c r="K242" t="n">
-        <v>1.922084617288877</v>
+        <v>1.92191103809226</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>13</v>
       </c>
       <c r="K243" t="n">
-        <v>1.835052498104472</v>
+        <v>1.835798003652634</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>13</v>
       </c>
       <c r="K244" t="n">
-        <v>1.781390400504812</v>
+        <v>1.784475424307148</v>
       </c>
     </row>
     <row r="245">
@@ -10486,7 +10486,7 @@
         <v>13</v>
       </c>
       <c r="K245" t="n">
-        <v>1.829442920342406</v>
+        <v>1.828069276243371</v>
       </c>
     </row>
     <row r="246">
@@ -10527,7 +10527,7 @@
         <v>13</v>
       </c>
       <c r="K246" t="n">
-        <v>1.829442920342406</v>
+        <v>1.828069276243371</v>
       </c>
     </row>
     <row r="247">
@@ -10568,7 +10568,7 @@
         <v>13</v>
       </c>
       <c r="K247" t="n">
-        <v>1.838879048398972</v>
+        <v>1.834755572047515</v>
       </c>
     </row>
     <row r="248">
@@ -10609,7 +10609,7 @@
         <v>13</v>
       </c>
       <c r="K248" t="n">
-        <v>1.862269297693542</v>
+        <v>1.866629638216385</v>
       </c>
     </row>
     <row r="249">
@@ -10650,7 +10650,7 @@
         <v>13</v>
       </c>
       <c r="K249" t="n">
-        <v>1.862269297693542</v>
+        <v>1.866629638216385</v>
       </c>
     </row>
     <row r="250">
@@ -10691,7 +10691,7 @@
         <v>13</v>
       </c>
       <c r="K250" t="n">
-        <v>1.992272159991618</v>
+        <v>1.99321973878386</v>
       </c>
     </row>
     <row r="251">
@@ -10732,7 +10732,7 @@
         <v>13</v>
       </c>
       <c r="K251" t="n">
-        <v>2.006304273811092</v>
+        <v>2.006174719754691</v>
       </c>
     </row>
     <row r="252">
@@ -10773,7 +10773,7 @@
         <v>13</v>
       </c>
       <c r="K252" t="n">
-        <v>1.979862095806364</v>
+        <v>1.978939815473383</v>
       </c>
     </row>
     <row r="253">
@@ -10814,7 +10814,7 @@
         <v>13</v>
       </c>
       <c r="K253" t="n">
-        <v>1.958232963266376</v>
+        <v>1.95864304861055</v>
       </c>
     </row>
     <row r="254">
@@ -10855,7 +10855,7 @@
         <v>13</v>
       </c>
       <c r="K254" t="n">
-        <v>1.958232963266376</v>
+        <v>1.95864304861055</v>
       </c>
     </row>
     <row r="255">
@@ -10896,7 +10896,7 @@
         <v>13</v>
       </c>
       <c r="K255" t="n">
-        <v>1.979860907556284</v>
+        <v>1.979755024362857</v>
       </c>
     </row>
     <row r="256">
@@ -10937,7 +10937,7 @@
         <v>13</v>
       </c>
       <c r="K256" t="n">
-        <v>1.97338395506932</v>
+        <v>1.973149157455507</v>
       </c>
     </row>
     <row r="257">
@@ -10978,7 +10978,7 @@
         <v>13</v>
       </c>
       <c r="K257" t="n">
-        <v>1.97338395506932</v>
+        <v>1.973149157455507</v>
       </c>
     </row>
     <row r="258">
@@ -11019,7 +11019,7 @@
         <v>13</v>
       </c>
       <c r="K258" t="n">
-        <v>2.094702487520755</v>
+        <v>2.095438247850818</v>
       </c>
     </row>
     <row r="259">
@@ -11060,7 +11060,7 @@
         <v>13</v>
       </c>
       <c r="K259" t="n">
-        <v>2.127189173542384</v>
+        <v>2.127723241738663</v>
       </c>
     </row>
     <row r="260">
@@ -11101,7 +11101,7 @@
         <v>13</v>
       </c>
       <c r="K260" t="n">
-        <v>2.139543690586782</v>
+        <v>2.139484458385704</v>
       </c>
     </row>
     <row r="261">
@@ -11142,7 +11142,7 @@
         <v>13</v>
       </c>
       <c r="K261" t="n">
-        <v>2.173726475012317</v>
+        <v>2.1743275034929</v>
       </c>
     </row>
     <row r="262">
@@ -11183,7 +11183,7 @@
         <v>13</v>
       </c>
       <c r="K262" t="n">
-        <v>2.19633243854267</v>
+        <v>2.196729542125996</v>
       </c>
     </row>
     <row r="263">
@@ -11224,7 +11224,7 @@
         <v>13</v>
       </c>
       <c r="K263" t="n">
-        <v>2.210980517993176</v>
+        <v>2.211229028313051</v>
       </c>
     </row>
     <row r="264">
@@ -11265,7 +11265,7 @@
         <v>13</v>
       </c>
       <c r="K264" t="n">
-        <v>2.23107155039617</v>
+        <v>2.231843139117101</v>
       </c>
     </row>
     <row r="265">
@@ -11306,7 +11306,7 @@
         <v>13</v>
       </c>
       <c r="K265" t="n">
-        <v>2.355335196847836</v>
+        <v>2.356652760710487</v>
       </c>
     </row>
     <row r="266">
@@ -11347,7 +11347,7 @@
         <v>13</v>
       </c>
       <c r="K266" t="n">
-        <v>2.416055884505181</v>
+        <v>2.417313127058556</v>
       </c>
     </row>
     <row r="267">
@@ -11388,7 +11388,7 @@
         <v>13</v>
       </c>
       <c r="K267" t="n">
-        <v>2.477853451311926</v>
+        <v>2.478944282467179</v>
       </c>
     </row>
     <row r="268">
@@ -11429,7 +11429,7 @@
         <v>13</v>
       </c>
       <c r="K268" t="n">
-        <v>2.569468355262374</v>
+        <v>2.57004333137354</v>
       </c>
     </row>
     <row r="269">
@@ -11470,7 +11470,7 @@
         <v>13</v>
       </c>
       <c r="K269" t="n">
-        <v>2.569468355262374</v>
+        <v>2.57004333137354</v>
       </c>
     </row>
     <row r="270">
@@ -11511,7 +11511,7 @@
         <v>13</v>
       </c>
       <c r="K270" t="n">
-        <v>2.644536362880819</v>
+        <v>2.645098986690952</v>
       </c>
     </row>
     <row r="271">
@@ -11552,7 +11552,7 @@
         <v>13</v>
       </c>
       <c r="K271" t="n">
-        <v>2.720452503598174</v>
+        <v>2.721636259979857</v>
       </c>
     </row>
     <row r="272">
@@ -11593,7 +11593,7 @@
         <v>13</v>
       </c>
       <c r="K272" t="n">
-        <v>2.82258817858393</v>
+        <v>2.822974639743892</v>
       </c>
     </row>
     <row r="273">
@@ -11634,7 +11634,7 @@
         <v>13</v>
       </c>
       <c r="K273" t="n">
-        <v>2.842201598260041</v>
+        <v>2.842342462532757</v>
       </c>
     </row>
     <row r="274">
@@ -11675,7 +11675,7 @@
         <v>13</v>
       </c>
       <c r="K274" t="n">
-        <v>2.863237632031469</v>
+        <v>2.862916897800067</v>
       </c>
     </row>
     <row r="275">
@@ -11716,7 +11716,7 @@
         <v>13</v>
       </c>
       <c r="K275" t="n">
-        <v>2.863237632031469</v>
+        <v>2.862916897800067</v>
       </c>
     </row>
     <row r="276">
@@ -11757,7 +11757,7 @@
         <v>13</v>
       </c>
       <c r="K276" t="n">
-        <v>2.935456735382338</v>
+        <v>2.935240705192184</v>
       </c>
     </row>
     <row r="277">
@@ -11798,7 +11798,7 @@
         <v>13</v>
       </c>
       <c r="K277" t="n">
-        <v>2.971304894385905</v>
+        <v>2.971704269926148</v>
       </c>
     </row>
     <row r="278">
@@ -11839,7 +11839,7 @@
         <v>13</v>
       </c>
       <c r="K278" t="n">
-        <v>2.996955943691693</v>
+        <v>2.997303175833328</v>
       </c>
     </row>
     <row r="279">
@@ -11880,7 +11880,7 @@
         <v>13</v>
       </c>
       <c r="K279" t="n">
-        <v>2.996955943691693</v>
+        <v>2.997303175833328</v>
       </c>
     </row>
     <row r="280">
@@ -11921,7 +11921,7 @@
         <v>13</v>
       </c>
       <c r="K280" t="n">
-        <v>2.888351156510363</v>
+        <v>2.889275235065853</v>
       </c>
     </row>
     <row r="281">
@@ -11962,7 +11962,7 @@
         <v>13</v>
       </c>
       <c r="K281" t="n">
-        <v>2.881999475913747</v>
+        <v>2.88133452874525</v>
       </c>
     </row>
     <row r="282">
@@ -12003,7 +12003,7 @@
         <v>13</v>
       </c>
       <c r="K282" t="n">
-        <v>2.881999475913747</v>
+        <v>2.88133452874525</v>
       </c>
     </row>
     <row r="283">
@@ -12044,7 +12044,7 @@
         <v>13</v>
       </c>
       <c r="K283" t="n">
-        <v>2.881999475913747</v>
+        <v>2.88133452874525</v>
       </c>
     </row>
     <row r="284">
@@ -12085,7 +12085,7 @@
         <v>13</v>
       </c>
       <c r="K284" t="n">
-        <v>2.931696851688956</v>
+        <v>2.934085449547536</v>
       </c>
     </row>
     <row r="285">
@@ -12126,7 +12126,7 @@
         <v>13</v>
       </c>
       <c r="K285" t="n">
-        <v>3.052324611637583</v>
+        <v>3.053645591692733</v>
       </c>
     </row>
     <row r="286">
@@ -12167,7 +12167,7 @@
         <v>13</v>
       </c>
       <c r="K286" t="n">
-        <v>3.117026603886375</v>
+        <v>3.118434197373088</v>
       </c>
     </row>
     <row r="287">
@@ -12208,7 +12208,7 @@
         <v>13</v>
       </c>
       <c r="K287" t="n">
-        <v>3.117026603886375</v>
+        <v>3.118434197373088</v>
       </c>
     </row>
     <row r="288">
@@ -12249,7 +12249,7 @@
         <v>13</v>
       </c>
       <c r="K288" t="n">
-        <v>3.220727790183071</v>
+        <v>3.220817863662048</v>
       </c>
     </row>
     <row r="289">
@@ -12290,7 +12290,7 @@
         <v>13</v>
       </c>
       <c r="K289" t="n">
-        <v>3.220727790183071</v>
+        <v>3.220817863662048</v>
       </c>
     </row>
     <row r="290">
@@ -12331,7 +12331,7 @@
         <v>13</v>
       </c>
       <c r="K290" t="n">
-        <v>3.206267301468427</v>
+        <v>3.206295793284919</v>
       </c>
     </row>
     <row r="291">
@@ -12372,7 +12372,7 @@
         <v>13</v>
       </c>
       <c r="K291" t="n">
-        <v>3.220069684849563</v>
+        <v>3.220114761613929</v>
       </c>
     </row>
     <row r="292">
@@ -12413,7 +12413,7 @@
         <v>13</v>
       </c>
       <c r="K292" t="n">
-        <v>3.220069684849563</v>
+        <v>3.220114761613929</v>
       </c>
     </row>
     <row r="293">
@@ -12454,7 +12454,7 @@
         <v>13</v>
       </c>
       <c r="K293" t="n">
-        <v>3.139266230842714</v>
+        <v>3.138656541129099</v>
       </c>
     </row>
     <row r="294">
@@ -12495,7 +12495,7 @@
         <v>13</v>
       </c>
       <c r="K294" t="n">
-        <v>3.051782695598409</v>
+        <v>3.051329111364734</v>
       </c>
     </row>
     <row r="295">
@@ -12536,7 +12536,7 @@
         <v>13</v>
       </c>
       <c r="K295" t="n">
-        <v>3.01812345520382</v>
+        <v>3.017515639191801</v>
       </c>
     </row>
     <row r="296">
@@ -12577,7 +12577,7 @@
         <v>13</v>
       </c>
       <c r="K296" t="n">
-        <v>2.950236123276051</v>
+        <v>2.950020202263393</v>
       </c>
     </row>
     <row r="297">
@@ -12618,7 +12618,7 @@
         <v>13</v>
       </c>
       <c r="K297" t="n">
-        <v>2.933064446758998</v>
+        <v>2.93302757224321</v>
       </c>
     </row>
     <row r="298">
@@ -12659,7 +12659,7 @@
         <v>13</v>
       </c>
       <c r="K298" t="n">
-        <v>2.969099575318594</v>
+        <v>2.969722246969912</v>
       </c>
     </row>
     <row r="299">
@@ -12700,7 +12700,7 @@
         <v>13</v>
       </c>
       <c r="K299" t="n">
-        <v>3.064871311042366</v>
+        <v>3.065467602927578</v>
       </c>
     </row>
     <row r="300">
@@ -12741,7 +12741,7 @@
         <v>13</v>
       </c>
       <c r="K300" t="n">
-        <v>3.114581492814289</v>
+        <v>3.115244885243321</v>
       </c>
     </row>
     <row r="301">
@@ -12782,7 +12782,7 @@
         <v>13</v>
       </c>
       <c r="K301" t="n">
-        <v>3.114581492814289</v>
+        <v>3.115244885243321</v>
       </c>
     </row>
     <row r="302">
@@ -12823,7 +12823,7 @@
         <v>13</v>
       </c>
       <c r="K302" t="n">
-        <v>3.209482865352926</v>
+        <v>3.209738267312777</v>
       </c>
     </row>
     <row r="303">
@@ -12864,7 +12864,7 @@
         <v>13</v>
       </c>
       <c r="K303" t="n">
-        <v>3.206758643135085</v>
+        <v>3.206467136474803</v>
       </c>
     </row>
     <row r="304">
@@ -12905,7 +12905,7 @@
         <v>13</v>
       </c>
       <c r="K304" t="n">
-        <v>3.056589363345596</v>
+        <v>3.055265449508024</v>
       </c>
     </row>
     <row r="305">
@@ -12946,7 +12946,7 @@
         <v>13</v>
       </c>
       <c r="K305" t="n">
-        <v>2.919437395450269</v>
+        <v>2.917899140912844</v>
       </c>
     </row>
     <row r="306">
@@ -12987,7 +12987,7 @@
         <v>13</v>
       </c>
       <c r="K306" t="n">
-        <v>2.611732014808289</v>
+        <v>2.61014864875598</v>
       </c>
     </row>
     <row r="307">
@@ -13028,7 +13028,7 @@
         <v>13</v>
       </c>
       <c r="K307" t="n">
-        <v>2.490075315065341</v>
+        <v>2.489522978381645</v>
       </c>
     </row>
     <row r="308">
@@ -13069,7 +13069,7 @@
         <v>13</v>
       </c>
       <c r="K308" t="n">
-        <v>2.490075315065341</v>
+        <v>2.489522978381645</v>
       </c>
     </row>
     <row r="309">
@@ -13110,7 +13110,7 @@
         <v>13</v>
       </c>
       <c r="K309" t="n">
-        <v>2.333084993733451</v>
+        <v>2.332837559119258</v>
       </c>
     </row>
     <row r="310">
@@ -13151,7 +13151,7 @@
         <v>13</v>
       </c>
       <c r="K310" t="n">
-        <v>2.470062220214085</v>
+        <v>2.470843054367419</v>
       </c>
     </row>
     <row r="311">
@@ -13192,7 +13192,7 @@
         <v>13</v>
       </c>
       <c r="K311" t="n">
-        <v>2.760853338379711</v>
+        <v>2.761356295213421</v>
       </c>
     </row>
     <row r="312">
@@ -13233,7 +13233,7 @@
         <v>13</v>
       </c>
       <c r="K312" t="n">
-        <v>2.831024448893697</v>
+        <v>2.831308172806444</v>
       </c>
     </row>
     <row r="313">
@@ -13274,7 +13274,7 @@
         <v>13</v>
       </c>
       <c r="K313" t="n">
-        <v>2.896485726977652</v>
+        <v>2.897062104598698</v>
       </c>
     </row>
     <row r="314">
@@ -13315,7 +13315,7 @@
         <v>13</v>
       </c>
       <c r="K314" t="n">
-        <v>3.138094025778499</v>
+        <v>3.138189352962061</v>
       </c>
     </row>
     <row r="315">
@@ -13356,7 +13356,7 @@
         <v>13</v>
       </c>
       <c r="K315" t="n">
-        <v>3.158030590125978</v>
+        <v>3.158055563698468</v>
       </c>
     </row>
     <row r="316">
@@ -13397,7 +13397,7 @@
         <v>13</v>
       </c>
       <c r="K316" t="n">
-        <v>2.957986706022475</v>
+        <v>2.957892247074617</v>
       </c>
     </row>
     <row r="317">
@@ -13438,7 +13438,7 @@
         <v>13</v>
       </c>
       <c r="K317" t="n">
-        <v>2.783391016408475</v>
+        <v>2.783385507469837</v>
       </c>
     </row>
     <row r="318">
@@ -13479,7 +13479,7 @@
         <v>13</v>
       </c>
       <c r="K318" t="n">
-        <v>2.781725254660016</v>
+        <v>2.781777704973392</v>
       </c>
     </row>
     <row r="319">
@@ -13520,7 +13520,7 @@
         <v>13</v>
       </c>
       <c r="K319" t="n">
-        <v>2.807824474919309</v>
+        <v>2.807883017886145</v>
       </c>
     </row>
     <row r="320">
@@ -13561,7 +13561,7 @@
         <v>13</v>
       </c>
       <c r="K320" t="n">
-        <v>2.807824474919309</v>
+        <v>2.807883017886145</v>
       </c>
     </row>
     <row r="321">
@@ -13602,7 +13602,7 @@
         <v>13</v>
       </c>
       <c r="K321" t="n">
-        <v>2.946118361960409</v>
+        <v>2.946128267523986</v>
       </c>
     </row>
     <row r="322">
@@ -13643,7 +13643,7 @@
         <v>13</v>
       </c>
       <c r="K322" t="n">
-        <v>2.959890013121888</v>
+        <v>2.959898248565642</v>
       </c>
     </row>
     <row r="323">
@@ -13684,7 +13684,7 @@
         <v>13</v>
       </c>
       <c r="K323" t="n">
-        <v>2.959890013121888</v>
+        <v>2.959898248565642</v>
       </c>
     </row>
     <row r="324">
@@ -13725,7 +13725,7 @@
         <v>13</v>
       </c>
       <c r="K324" t="n">
-        <v>2.920106593276818</v>
+        <v>2.920147948372866</v>
       </c>
     </row>
     <row r="325">
@@ -13766,7 +13766,7 @@
         <v>13</v>
       </c>
       <c r="K325" t="n">
-        <v>2.824455462485941</v>
+        <v>2.824611422705501</v>
       </c>
     </row>
     <row r="326">
@@ -13807,7 +13807,7 @@
         <v>13</v>
       </c>
       <c r="K326" t="n">
-        <v>2.694576033673506</v>
+        <v>2.694812092533257</v>
       </c>
     </row>
     <row r="327">
@@ -13848,7 +13848,7 @@
         <v>13</v>
       </c>
       <c r="K327" t="n">
-        <v>2.542914879365028</v>
+        <v>2.543179224416091</v>
       </c>
     </row>
     <row r="328">
@@ -13889,7 +13889,7 @@
         <v>13</v>
       </c>
       <c r="K328" t="n">
-        <v>2.542914879365028</v>
+        <v>2.543179224416091</v>
       </c>
     </row>
     <row r="329">
@@ -13930,7 +13930,7 @@
         <v>13</v>
       </c>
       <c r="K329" t="n">
-        <v>2.388320281588208</v>
+        <v>2.388615791877871</v>
       </c>
     </row>
     <row r="330">
@@ -13971,7 +13971,7 @@
         <v>13</v>
       </c>
       <c r="K330" t="n">
-        <v>2.059868044147878</v>
+        <v>2.060296401669989</v>
       </c>
     </row>
     <row r="331">
@@ -14012,7 +14012,7 @@
         <v>13</v>
       </c>
       <c r="K331" t="n">
-        <v>1.90235679214078</v>
+        <v>1.902807076535521</v>
       </c>
     </row>
     <row r="332">
@@ -14053,7 +14053,7 @@
         <v>13</v>
       </c>
       <c r="K332" t="n">
-        <v>1.90235679214078</v>
+        <v>1.902807076535521</v>
       </c>
     </row>
     <row r="333">
@@ -14094,7 +14094,7 @@
         <v>13</v>
       </c>
       <c r="K333" t="n">
-        <v>1.721349577604772</v>
+        <v>1.721448865094933</v>
       </c>
     </row>
     <row r="334">
@@ -14135,7 +14135,7 @@
         <v>13</v>
       </c>
       <c r="K334" t="n">
-        <v>1.698503598909412</v>
+        <v>1.698581797938946</v>
       </c>
     </row>
     <row r="335">
@@ -14176,7 +14176,7 @@
         <v>13</v>
       </c>
       <c r="K335" t="n">
-        <v>1.651663073750607</v>
+        <v>1.651722498352377</v>
       </c>
     </row>
     <row r="336">
@@ -14217,7 +14217,7 @@
         <v>13</v>
       </c>
       <c r="K336" t="n">
-        <v>1.640962655131619</v>
+        <v>1.641023329838015</v>
       </c>
     </row>
     <row r="337">
@@ -14258,7 +14258,7 @@
         <v>13</v>
       </c>
       <c r="K337" t="n">
-        <v>1.561481941261449</v>
+        <v>1.561564714197528</v>
       </c>
     </row>
     <row r="338">
@@ -14299,7 +14299,7 @@
         <v>13</v>
       </c>
       <c r="K338" t="n">
-        <v>1.553402052511876</v>
+        <v>1.553747736935322</v>
       </c>
     </row>
     <row r="339">
@@ -14340,7 +14340,7 @@
         <v>13</v>
       </c>
       <c r="K339" t="n">
-        <v>1.553402052511876</v>
+        <v>1.553747736935322</v>
       </c>
     </row>
     <row r="340">
@@ -14381,7 +14381,7 @@
         <v>13</v>
       </c>
       <c r="K340" t="n">
-        <v>1.558134622278291</v>
+        <v>1.559018042951869</v>
       </c>
     </row>
     <row r="341">
@@ -14422,7 +14422,7 @@
         <v>13</v>
       </c>
       <c r="K341" t="n">
-        <v>1.592535875313988</v>
+        <v>1.591962604231321</v>
       </c>
     </row>
     <row r="342">
@@ -14463,7 +14463,7 @@
         <v>13</v>
       </c>
       <c r="K342" t="n">
-        <v>1.581930598851415</v>
+        <v>1.58219116468158</v>
       </c>
     </row>
     <row r="343">
@@ -14504,7 +14504,7 @@
         <v>13</v>
       </c>
       <c r="K343" t="n">
-        <v>1.581930598851415</v>
+        <v>1.58219116468158</v>
       </c>
     </row>
     <row r="344">
@@ -14545,7 +14545,7 @@
         <v>13</v>
       </c>
       <c r="K344" t="n">
-        <v>1.568189773827232</v>
+        <v>1.568263459788325</v>
       </c>
     </row>
     <row r="345">
@@ -14586,7 +14586,7 @@
         <v>13</v>
       </c>
       <c r="K345" t="n">
-        <v>1.568189773827232</v>
+        <v>1.568263459788325</v>
       </c>
     </row>
     <row r="346">
@@ -14627,7 +14627,7 @@
         <v>13</v>
       </c>
       <c r="K346" t="n">
-        <v>1.536087651858876</v>
+        <v>1.53550009660177</v>
       </c>
     </row>
     <row r="347">
@@ -14668,7 +14668,7 @@
         <v>13</v>
       </c>
       <c r="K347" t="n">
-        <v>1.567914364678312</v>
+        <v>1.567801121767118</v>
       </c>
     </row>
     <row r="348">
@@ -14709,7 +14709,7 @@
         <v>13</v>
       </c>
       <c r="K348" t="n">
-        <v>1.952976055882561</v>
+        <v>1.952513172025594</v>
       </c>
     </row>
     <row r="349">
@@ -14750,7 +14750,7 @@
         <v>13</v>
       </c>
       <c r="K349" t="n">
-        <v>1.952976055882561</v>
+        <v>1.952513172025594</v>
       </c>
     </row>
     <row r="350">
@@ -14791,7 +14791,7 @@
         <v>13</v>
       </c>
       <c r="K350" t="n">
-        <v>1.952976055882561</v>
+        <v>1.952513172025594</v>
       </c>
     </row>
     <row r="351">
@@ -14832,7 +14832,7 @@
         <v>13</v>
       </c>
       <c r="K351" t="n">
-        <v>2.494303518880437</v>
+        <v>2.499116316829227</v>
       </c>
     </row>
     <row r="352">
@@ -14873,7 +14873,7 @@
         <v>13</v>
       </c>
       <c r="K352" t="n">
-        <v>2.765479861290443</v>
+        <v>2.769724224455324</v>
       </c>
     </row>
     <row r="353">
@@ -14914,7 +14914,7 @@
         <v>13</v>
       </c>
       <c r="K353" t="n">
-        <v>2.765479861290443</v>
+        <v>2.769724224455324</v>
       </c>
     </row>
     <row r="354">
@@ -14955,7 +14955,7 @@
         <v>13</v>
       </c>
       <c r="K354" t="n">
-        <v>2.765479861290443</v>
+        <v>2.769724224455324</v>
       </c>
     </row>
     <row r="355">
@@ -14996,7 +14996,7 @@
         <v>13</v>
       </c>
       <c r="K355" t="n">
-        <v>3.046028552446972</v>
+        <v>3.036197259515079</v>
       </c>
     </row>
     <row r="356">
@@ -15037,7 +15037,7 @@
         <v>13</v>
       </c>
       <c r="K356" t="n">
-        <v>3.100813226182276</v>
+        <v>3.085142127216123</v>
       </c>
     </row>
     <row r="357">
@@ -15078,7 +15078,7 @@
         <v>13</v>
       </c>
       <c r="K357" t="n">
-        <v>2.828640373609562</v>
+        <v>2.827265404589385</v>
       </c>
     </row>
     <row r="358">
@@ -15119,7 +15119,7 @@
         <v>13</v>
       </c>
       <c r="K358" t="n">
-        <v>2.828640373609562</v>
+        <v>2.827265404589385</v>
       </c>
     </row>
     <row r="359">
@@ -15160,7 +15160,7 @@
         <v>13</v>
       </c>
       <c r="K359" t="n">
-        <v>2.731107144267778</v>
+        <v>2.728816741614861</v>
       </c>
     </row>
     <row r="360">
@@ -15201,7 +15201,7 @@
         <v>13</v>
       </c>
       <c r="K360" t="n">
-        <v>2.483879001518723</v>
+        <v>2.482361445327758</v>
       </c>
     </row>
     <row r="361">
@@ -15242,7 +15242,7 @@
         <v>13</v>
       </c>
       <c r="K361" t="n">
-        <v>2.483879001518723</v>
+        <v>2.482361445327758</v>
       </c>
     </row>
     <row r="362">
@@ -15283,7 +15283,7 @@
         <v>13</v>
       </c>
       <c r="K362" t="n">
-        <v>2.483879001518723</v>
+        <v>2.482361445327758</v>
       </c>
     </row>
     <row r="363">
@@ -15324,7 +15324,7 @@
         <v>13</v>
       </c>
       <c r="K363" t="n">
-        <v>2.380256929299152</v>
+        <v>2.379803869920021</v>
       </c>
     </row>
     <row r="364">
@@ -15365,7 +15365,7 @@
         <v>13</v>
       </c>
       <c r="K364" t="n">
-        <v>2.361346344683295</v>
+        <v>2.361570330523162</v>
       </c>
     </row>
     <row r="365">
@@ -15406,7 +15406,7 @@
         <v>13</v>
       </c>
       <c r="K365" t="n">
-        <v>2.372434835599062</v>
+        <v>2.373110160922415</v>
       </c>
     </row>
     <row r="366">
@@ -15447,7 +15447,7 @@
         <v>13</v>
       </c>
       <c r="K366" t="n">
-        <v>2.345564094498081</v>
+        <v>2.343777247319016</v>
       </c>
     </row>
     <row r="367">
@@ -15488,7 +15488,7 @@
         <v>13</v>
       </c>
       <c r="K367" t="n">
-        <v>2.213527183372355</v>
+        <v>2.211612152272882</v>
       </c>
     </row>
     <row r="368">
@@ -15529,7 +15529,7 @@
         <v>13</v>
       </c>
       <c r="K368" t="n">
-        <v>1.975941673361365</v>
+        <v>1.973501817706361</v>
       </c>
     </row>
     <row r="369">
@@ -15570,7 +15570,7 @@
         <v>13</v>
       </c>
       <c r="K369" t="n">
-        <v>1.975941673361365</v>
+        <v>1.973501817706361</v>
       </c>
     </row>
     <row r="370">
@@ -15611,7 +15611,7 @@
         <v>13</v>
       </c>
       <c r="K370" t="n">
-        <v>1.865613372365461</v>
+        <v>1.862853427685387</v>
       </c>
     </row>
     <row r="371">
@@ -15652,7 +15652,7 @@
         <v>13</v>
       </c>
       <c r="K371" t="n">
-        <v>1.666097909423621</v>
+        <v>1.663940106505621</v>
       </c>
     </row>
     <row r="372">
@@ -15693,7 +15693,7 @@
         <v>13</v>
       </c>
       <c r="K372" t="n">
-        <v>1.506313009646927</v>
+        <v>1.505003376497279</v>
       </c>
     </row>
     <row r="373">
@@ -15734,7 +15734,7 @@
         <v>13</v>
       </c>
       <c r="K373" t="n">
-        <v>1.506313009646927</v>
+        <v>1.505003376497279</v>
       </c>
     </row>
     <row r="374">
@@ -15775,7 +15775,7 @@
         <v>13</v>
       </c>
       <c r="K374" t="n">
-        <v>1.449329550034161</v>
+        <v>1.448088484355862</v>
       </c>
     </row>
     <row r="375">
@@ -15816,7 +15816,7 @@
         <v>13</v>
       </c>
       <c r="K375" t="n">
-        <v>1.397985058834273</v>
+        <v>1.396923049925755</v>
       </c>
     </row>
     <row r="376">
@@ -15857,7 +15857,7 @@
         <v>13</v>
       </c>
       <c r="K376" t="n">
-        <v>1.351557030145482</v>
+        <v>1.350691115238399</v>
       </c>
     </row>
     <row r="377">
@@ -15898,7 +15898,7 @@
         <v>13</v>
       </c>
       <c r="K377" t="n">
-        <v>1.305351778442707</v>
+        <v>1.305213057231433</v>
       </c>
     </row>
     <row r="378">
@@ -15939,7 +15939,7 @@
         <v>13</v>
       </c>
       <c r="K378" t="n">
-        <v>1.298901247902165</v>
+        <v>1.298816464360101</v>
       </c>
     </row>
     <row r="379">
@@ -15980,7 +15980,7 @@
         <v>13</v>
       </c>
       <c r="K379" t="n">
-        <v>1.325150959140536</v>
+        <v>1.325453158197683</v>
       </c>
     </row>
     <row r="380">
@@ -16021,7 +16021,7 @@
         <v>13</v>
       </c>
       <c r="K380" t="n">
-        <v>1.415467175486323</v>
+        <v>1.416263612450175</v>
       </c>
     </row>
     <row r="381">
@@ -16062,7 +16062,7 @@
         <v>13</v>
       </c>
       <c r="K381" t="n">
-        <v>1.468564760461942</v>
+        <v>1.469614919805588</v>
       </c>
     </row>
     <row r="382">
@@ -16103,7 +16103,7 @@
         <v>13</v>
       </c>
       <c r="K382" t="n">
-        <v>1.53165346771304</v>
+        <v>1.532838109281079</v>
       </c>
     </row>
     <row r="383">
@@ -16144,7 +16144,7 @@
         <v>13</v>
       </c>
       <c r="K383" t="n">
-        <v>1.605584350685485</v>
+        <v>1.606968434449884</v>
       </c>
     </row>
     <row r="384">
@@ -16185,7 +16185,7 @@
         <v>13</v>
       </c>
       <c r="K384" t="n">
-        <v>1.839479514257422</v>
+        <v>1.840656012138715</v>
       </c>
     </row>
     <row r="385">
@@ -16226,7 +16226,7 @@
         <v>13</v>
       </c>
       <c r="K385" t="n">
-        <v>1.907695024717555</v>
+        <v>1.908715244955446</v>
       </c>
     </row>
     <row r="386">
@@ -16267,7 +16267,7 @@
         <v>13</v>
       </c>
       <c r="K386" t="n">
-        <v>1.907695024717555</v>
+        <v>1.908715244955446</v>
       </c>
     </row>
     <row r="387">
@@ -16308,7 +16308,7 @@
         <v>13</v>
       </c>
       <c r="K387" t="n">
-        <v>2.098392900454576</v>
+        <v>2.098867255156686</v>
       </c>
     </row>
     <row r="388">
@@ -16349,7 +16349,7 @@
         <v>13</v>
       </c>
       <c r="K388" t="n">
-        <v>2.125893996626484</v>
+        <v>2.12619444005531</v>
       </c>
     </row>
     <row r="389">
@@ -16390,7 +16390,7 @@
         <v>13</v>
       </c>
       <c r="K389" t="n">
-        <v>2.156690347619346</v>
+        <v>2.156638538462119</v>
       </c>
     </row>
     <row r="390">
@@ -16431,7 +16431,7 @@
         <v>13</v>
       </c>
       <c r="K390" t="n">
-        <v>2.144931093967293</v>
+        <v>2.144562660636978</v>
       </c>
     </row>
     <row r="391">
@@ -16472,7 +16472,7 @@
         <v>13</v>
       </c>
       <c r="K391" t="n">
-        <v>2.144931093967293</v>
+        <v>2.144562660636978</v>
       </c>
     </row>
     <row r="392">
@@ -16513,7 +16513,7 @@
         <v>13</v>
       </c>
       <c r="K392" t="n">
-        <v>1.977705179743598</v>
+        <v>1.977268740536044</v>
       </c>
     </row>
     <row r="393">
@@ -16554,7 +16554,7 @@
         <v>13</v>
       </c>
       <c r="K393" t="n">
-        <v>1.977705179743598</v>
+        <v>1.977268740536044</v>
       </c>
     </row>
     <row r="394">
@@ -16595,7 +16595,7 @@
         <v>13</v>
       </c>
       <c r="K394" t="n">
-        <v>1.876517727390925</v>
+        <v>1.876157890759888</v>
       </c>
     </row>
     <row r="395">
@@ -16636,7 +16636,7 @@
         <v>13</v>
       </c>
       <c r="K395" t="n">
-        <v>1.793464093134713</v>
+        <v>1.793274421579458</v>
       </c>
     </row>
     <row r="396">
@@ -16677,7 +16677,7 @@
         <v>13</v>
       </c>
       <c r="K396" t="n">
-        <v>1.793464093134713</v>
+        <v>1.793274421579458</v>
       </c>
     </row>
     <row r="397">
@@ -16718,7 +16718,7 @@
         <v>13</v>
       </c>
       <c r="K397" t="n">
-        <v>1.777659199519649</v>
+        <v>1.777676743680832</v>
       </c>
     </row>
     <row r="398">
@@ -16759,7 +16759,7 @@
         <v>13</v>
       </c>
       <c r="K398" t="n">
-        <v>1.8015959309684</v>
+        <v>1.80153322644804</v>
       </c>
     </row>
     <row r="399">
@@ -16800,7 +16800,7 @@
         <v>13</v>
       </c>
       <c r="K399" t="n">
-        <v>1.8015959309684</v>
+        <v>1.80153322644804</v>
       </c>
     </row>
     <row r="400">
@@ -16841,7 +16841,7 @@
         <v>13</v>
       </c>
       <c r="K400" t="n">
-        <v>1.781521394405934</v>
+        <v>1.781276938526397</v>
       </c>
     </row>
     <row r="401">
@@ -16882,7 +16882,7 @@
         <v>13</v>
       </c>
       <c r="K401" t="n">
-        <v>1.707767716195527</v>
+        <v>1.707583330638225</v>
       </c>
     </row>
     <row r="402">
@@ -16923,7 +16923,7 @@
         <v>13</v>
       </c>
       <c r="K402" t="n">
-        <v>1.676679034812198</v>
+        <v>1.676473911377473</v>
       </c>
     </row>
     <row r="403">
@@ -16964,7 +16964,7 @@
         <v>13</v>
       </c>
       <c r="K403" t="n">
-        <v>1.676679034812198</v>
+        <v>1.676473911377473</v>
       </c>
     </row>
     <row r="404">
@@ -17005,7 +17005,7 @@
         <v>13</v>
       </c>
       <c r="K404" t="n">
-        <v>1.588453590568637</v>
+        <v>1.588408942685642</v>
       </c>
     </row>
     <row r="405">
@@ -17046,7 +17046,7 @@
         <v>13</v>
       </c>
       <c r="K405" t="n">
-        <v>1.541416976561704</v>
+        <v>1.541179223697354</v>
       </c>
     </row>
     <row r="406">
@@ -17087,7 +17087,7 @@
         <v>13</v>
       </c>
       <c r="K406" t="n">
-        <v>1.461973390111028</v>
+        <v>1.462133213544843</v>
       </c>
     </row>
     <row r="407">
@@ -17128,7 +17128,7 @@
         <v>13</v>
       </c>
       <c r="K407" t="n">
-        <v>1.461973390111028</v>
+        <v>1.462133213544843</v>
       </c>
     </row>
     <row r="408">
@@ -17169,7 +17169,7 @@
         <v>13</v>
       </c>
       <c r="K408" t="n">
-        <v>1.299924719804793</v>
+        <v>1.298218895985838</v>
       </c>
     </row>
     <row r="409">
@@ -17210,7 +17210,7 @@
         <v>13</v>
       </c>
       <c r="K409" t="n">
-        <v>1.299924719804793</v>
+        <v>1.298218895985838</v>
       </c>
     </row>
     <row r="410">
@@ -17251,7 +17251,7 @@
         <v>13</v>
       </c>
       <c r="K410" t="n">
-        <v>1.299924719804793</v>
+        <v>1.298218895985838</v>
       </c>
     </row>
     <row r="411">
@@ -17292,7 +17292,7 @@
         <v>13</v>
       </c>
       <c r="K411" t="n">
-        <v>1.234009848682012</v>
+        <v>1.298218895985838</v>
       </c>
     </row>
     <row r="412">
@@ -17333,7 +17333,7 @@
         <v>13</v>
       </c>
       <c r="K412" t="n">
-        <v>1.234009848682012</v>
+        <v>1.231889797743272</v>
       </c>
     </row>
     <row r="413">
@@ -17374,7 +17374,7 @@
         <v>13</v>
       </c>
       <c r="K413" t="n">
-        <v>1.163607608399603</v>
+        <v>1.163956498041505</v>
       </c>
     </row>
     <row r="414">
@@ -17415,7 +17415,7 @@
         <v>13</v>
       </c>
       <c r="K414" t="n">
-        <v>1.108748276134141</v>
+        <v>1.107307130803022</v>
       </c>
     </row>
     <row r="415">
@@ -17456,7 +17456,7 @@
         <v>13</v>
       </c>
       <c r="K415" t="n">
-        <v>1.108748276134141</v>
+        <v>1.107307130803022</v>
       </c>
     </row>
     <row r="416">
@@ -17497,7 +17497,7 @@
         <v>13</v>
       </c>
       <c r="K416" t="n">
-        <v>1.108748276134141</v>
+        <v>1.107307130803022</v>
       </c>
     </row>
     <row r="417">
@@ -17538,7 +17538,7 @@
         <v>13</v>
       </c>
       <c r="K417" t="n">
-        <v>1.143908926624225</v>
+        <v>1.143930311031932</v>
       </c>
     </row>
     <row r="418">
@@ -17579,7 +17579,7 @@
         <v>13</v>
       </c>
       <c r="K418" t="n">
-        <v>1.143908926624225</v>
+        <v>1.143930311031932</v>
       </c>
     </row>
     <row r="419">
@@ -17620,7 +17620,7 @@
         <v>13</v>
       </c>
       <c r="K419" t="n">
-        <v>1.17283296788326</v>
+        <v>1.172889400054853</v>
       </c>
     </row>
     <row r="420">
@@ -17661,7 +17661,7 @@
         <v>13</v>
       </c>
       <c r="K420" t="n">
-        <v>1.197101282903176</v>
+        <v>1.197256910262096</v>
       </c>
     </row>
     <row r="421">
@@ -17702,7 +17702,7 @@
         <v>13</v>
       </c>
       <c r="K421" t="n">
-        <v>1.340723206750572</v>
+        <v>1.340839851242881</v>
       </c>
     </row>
     <row r="422">
@@ -17743,7 +17743,7 @@
         <v>13</v>
       </c>
       <c r="K422" t="n">
-        <v>1.387922623419854</v>
+        <v>1.388011820329891</v>
       </c>
     </row>
     <row r="423">
@@ -17784,7 +17784,7 @@
         <v>13</v>
       </c>
       <c r="K423" t="n">
-        <v>1.528974275552455</v>
+        <v>1.528966677935175</v>
       </c>
     </row>
     <row r="424">
@@ -17825,7 +17825,7 @@
         <v>13</v>
       </c>
       <c r="K424" t="n">
-        <v>1.528974275552455</v>
+        <v>1.528966677935175</v>
       </c>
     </row>
     <row r="425">
@@ -17866,7 +17866,7 @@
         <v>13</v>
       </c>
       <c r="K425" t="n">
-        <v>1.528974275552455</v>
+        <v>1.528966677935175</v>
       </c>
     </row>
     <row r="426">
@@ -17907,7 +17907,7 @@
         <v>13</v>
       </c>
       <c r="K426" t="n">
-        <v>1.519678996391473</v>
+        <v>1.519626370871193</v>
       </c>
     </row>
   </sheetData>
